--- a/research/traditional_assets/database/data/finland/finland_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_drugs_pharmaceutical.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0887999538907096</v>
+        <v>0.08865835398292818</v>
       </c>
       <c r="C2">
-        <v>6443.369887875351</v>
+        <v>6397.822318044637</v>
       </c>
       <c r="D2">
-        <v>6231.369887875351</v>
+        <v>6250.853318044637</v>
       </c>
       <c r="E2">
-        <v>-286.4</v>
+        <v>-221.369</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65.03099999999999</v>
       </c>
       <c r="G2">
         <v>212</v>
@@ -1582,28 +1582,28 @@
         <v>423.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.271059299999999</v>
       </c>
       <c r="N2">
-        <v>423.4</v>
+        <v>420.1289407</v>
       </c>
       <c r="O2">
-        <v>84.68000000000001</v>
+        <v>84.02578814</v>
       </c>
       <c r="P2">
-        <v>338.72</v>
+        <v>336.10315256</v>
       </c>
       <c r="Q2">
-        <v>390.42</v>
+        <v>387.8031525600001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0887999538907096</v>
+        <v>0.08914742826558403</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8912687490991633</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>129.4381914751592</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08865835398292818</v>
+        <v>0.08851675407514675</v>
       </c>
       <c r="C3">
-        <v>6397.822318044637</v>
+        <v>6352.396966819734</v>
       </c>
       <c r="D3">
-        <v>6250.853318044637</v>
+        <v>6270.458966819734</v>
       </c>
       <c r="E3">
-        <v>-221.369</v>
+        <v>-156.338</v>
       </c>
       <c r="F3">
-        <v>65.03099999999999</v>
+        <v>130.062</v>
       </c>
       <c r="G3">
         <v>212</v>
@@ -1664,28 +1664,28 @@
         <v>423.4</v>
       </c>
       <c r="M3">
-        <v>3.271059299999999</v>
+        <v>6.542118599999998</v>
       </c>
       <c r="N3">
-        <v>420.1289407</v>
+        <v>416.8578814</v>
       </c>
       <c r="O3">
-        <v>84.02578814</v>
+        <v>83.37157628</v>
       </c>
       <c r="P3">
-        <v>336.10315256</v>
+        <v>333.48630512</v>
       </c>
       <c r="Q3">
-        <v>387.8031525600001</v>
+        <v>385.18630512</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08914742826558403</v>
+        <v>0.08950199395423139</v>
       </c>
       <c r="T3">
-        <v>0.8912687490991633</v>
+        <v>0.8985589928446065</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.4381914751592</v>
+        <v>64.71909573757958</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08851675407514675</v>
+        <v>0.08837515416736534</v>
       </c>
       <c r="C4">
-        <v>6352.396966819734</v>
+        <v>6307.094987825975</v>
       </c>
       <c r="D4">
-        <v>6270.458966819734</v>
+        <v>6290.187987825975</v>
       </c>
       <c r="E4">
-        <v>-156.338</v>
+        <v>-91.30699999999999</v>
       </c>
       <c r="F4">
-        <v>130.062</v>
+        <v>195.093</v>
       </c>
       <c r="G4">
         <v>212</v>
@@ -1746,28 +1746,28 @@
         <v>423.4</v>
       </c>
       <c r="M4">
-        <v>6.542118599999998</v>
+        <v>9.813177899999999</v>
       </c>
       <c r="N4">
-        <v>416.8578814</v>
+        <v>413.5868220999999</v>
       </c>
       <c r="O4">
-        <v>83.37157628</v>
+        <v>82.71736442</v>
       </c>
       <c r="P4">
-        <v>333.48630512</v>
+        <v>330.86945768</v>
       </c>
       <c r="Q4">
-        <v>385.18630512</v>
+        <v>382.56945768</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08950199395423139</v>
+        <v>0.08986387027563437</v>
       </c>
       <c r="T4">
-        <v>0.8985589928446065</v>
+        <v>0.9059995508940795</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.71909573757958</v>
+        <v>43.14606382505304</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08837515416736534</v>
+        <v>0.08823355425958393</v>
       </c>
       <c r="C5">
-        <v>6307.094987825975</v>
+        <v>6261.917549253332</v>
       </c>
       <c r="D5">
-        <v>6290.187987825975</v>
+        <v>6310.041549253332</v>
       </c>
       <c r="E5">
-        <v>-91.30699999999999</v>
+        <v>-26.27600000000001</v>
       </c>
       <c r="F5">
-        <v>195.093</v>
+        <v>260.124</v>
       </c>
       <c r="G5">
         <v>212</v>
@@ -1828,28 +1828,28 @@
         <v>423.4</v>
       </c>
       <c r="M5">
-        <v>9.813177899999999</v>
+        <v>13.0842372</v>
       </c>
       <c r="N5">
-        <v>413.5868220999999</v>
+        <v>410.3157628</v>
       </c>
       <c r="O5">
-        <v>82.71736442</v>
+        <v>82.06315255999999</v>
       </c>
       <c r="P5">
-        <v>330.86945768</v>
+        <v>328.25261024</v>
       </c>
       <c r="Q5">
-        <v>382.56945768</v>
+        <v>379.95261024</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08986387027563437</v>
+        <v>0.09023328568706659</v>
       </c>
       <c r="T5">
-        <v>0.9059995508940795</v>
+        <v>0.9135951205695833</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.14606382505304</v>
+        <v>32.35954786878979</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08823355425958393</v>
+        <v>0.0880919543518025</v>
       </c>
       <c r="C6">
-        <v>6261.917549253332</v>
+        <v>6216.865834086987</v>
       </c>
       <c r="D6">
-        <v>6310.041549253332</v>
+        <v>6330.020834086987</v>
       </c>
       <c r="E6">
-        <v>-26.27600000000001</v>
+        <v>38.755</v>
       </c>
       <c r="F6">
-        <v>260.124</v>
+        <v>325.155</v>
       </c>
       <c r="G6">
         <v>212</v>
@@ -1910,28 +1910,28 @@
         <v>423.4</v>
       </c>
       <c r="M6">
-        <v>13.0842372</v>
+        <v>16.3552965</v>
       </c>
       <c r="N6">
-        <v>410.3157628</v>
+        <v>407.0447035</v>
       </c>
       <c r="O6">
-        <v>82.06315255999999</v>
+        <v>81.4089407</v>
       </c>
       <c r="P6">
-        <v>328.25261024</v>
+        <v>325.6357628</v>
       </c>
       <c r="Q6">
-        <v>379.95261024</v>
+        <v>377.3357628</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09023328568706659</v>
+        <v>0.09061047826505528</v>
       </c>
       <c r="T6">
-        <v>0.9135951205695833</v>
+        <v>0.9213505969750975</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.35954786878979</v>
+        <v>25.88763829503183</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0880919543518025</v>
+        <v>0.08795035444402109</v>
       </c>
       <c r="C7">
-        <v>6216.865834086987</v>
+        <v>6171.9410403423</v>
       </c>
       <c r="D7">
-        <v>6330.020834086987</v>
+        <v>6350.1270403423</v>
       </c>
       <c r="E7">
-        <v>38.755</v>
+        <v>103.786</v>
       </c>
       <c r="F7">
-        <v>325.155</v>
+        <v>390.186</v>
       </c>
       <c r="G7">
         <v>212</v>
@@ -1992,28 +1992,28 @@
         <v>423.4</v>
       </c>
       <c r="M7">
-        <v>16.3552965</v>
+        <v>19.6263558</v>
       </c>
       <c r="N7">
-        <v>407.0447035</v>
+        <v>403.7736442</v>
       </c>
       <c r="O7">
-        <v>81.4089407</v>
+        <v>80.75472884</v>
       </c>
       <c r="P7">
-        <v>325.6357628</v>
+        <v>323.01891536</v>
       </c>
       <c r="Q7">
-        <v>377.3357628</v>
+        <v>374.71891536</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09061047826505528</v>
+        <v>0.09099569621704372</v>
       </c>
       <c r="T7">
-        <v>0.9213505969750975</v>
+        <v>0.9292710835168994</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.88763829503183</v>
+        <v>21.57303191252652</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08795035444402109</v>
+        <v>0.08780875453623967</v>
       </c>
       <c r="C8">
-        <v>6171.9410403423</v>
+        <v>6127.144381304287</v>
       </c>
       <c r="D8">
-        <v>6350.1270403423</v>
+        <v>6370.361381304287</v>
       </c>
       <c r="E8">
-        <v>103.786</v>
+        <v>168.817</v>
       </c>
       <c r="F8">
-        <v>390.186</v>
+        <v>455.2169999999999</v>
       </c>
       <c r="G8">
         <v>212</v>
@@ -2074,28 +2074,28 @@
         <v>423.4</v>
       </c>
       <c r="M8">
-        <v>19.6263558</v>
+        <v>22.8974151</v>
       </c>
       <c r="N8">
-        <v>403.7736442</v>
+        <v>400.5025849</v>
       </c>
       <c r="O8">
-        <v>80.75472884</v>
+        <v>80.10051698000001</v>
       </c>
       <c r="P8">
-        <v>323.01891536</v>
+        <v>320.40206792</v>
       </c>
       <c r="Q8">
-        <v>374.71891536</v>
+        <v>372.10206792</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09099569621704372</v>
+        <v>0.09138919842606416</v>
       </c>
       <c r="T8">
-        <v>0.9292710835168994</v>
+        <v>0.9373619031026109</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.57303191252652</v>
+        <v>18.49117021073702</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08780875453623965</v>
+        <v>0.08766715462845827</v>
       </c>
       <c r="C9">
-        <v>6127.144381304289</v>
+        <v>6082.477085771659</v>
       </c>
       <c r="D9">
-        <v>6370.361381304288</v>
+        <v>6390.725085771659</v>
       </c>
       <c r="E9">
-        <v>168.817</v>
+        <v>233.848</v>
       </c>
       <c r="F9">
-        <v>455.217</v>
+        <v>520.2479999999999</v>
       </c>
       <c r="G9">
         <v>212</v>
@@ -2156,28 +2156,28 @@
         <v>423.4</v>
       </c>
       <c r="M9">
-        <v>22.8974151</v>
+        <v>26.16847439999999</v>
       </c>
       <c r="N9">
-        <v>400.5025849</v>
+        <v>397.2315256</v>
       </c>
       <c r="O9">
-        <v>80.10051698000001</v>
+        <v>79.44630512000001</v>
       </c>
       <c r="P9">
-        <v>320.40206792</v>
+        <v>317.78522048</v>
       </c>
       <c r="Q9">
-        <v>372.10206792</v>
+        <v>369.4852204800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09138919842606416</v>
+        <v>0.09179125503093288</v>
       </c>
       <c r="T9">
-        <v>0.9373619031026109</v>
+        <v>0.9456286100706205</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.49117021073702</v>
+        <v>16.17977393439489</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08766715462845827</v>
+        <v>0.08752555472067683</v>
       </c>
       <c r="C10">
-        <v>6082.477085771659</v>
+        <v>6037.940398305604</v>
       </c>
       <c r="D10">
-        <v>6390.725085771659</v>
+        <v>6411.219398305603</v>
       </c>
       <c r="E10">
-        <v>233.848</v>
+        <v>298.8789999999999</v>
       </c>
       <c r="F10">
-        <v>520.2479999999999</v>
+        <v>585.2789999999999</v>
       </c>
       <c r="G10">
         <v>212</v>
@@ -2238,28 +2238,28 @@
         <v>423.4</v>
       </c>
       <c r="M10">
-        <v>26.16847439999999</v>
+        <v>29.43953369999999</v>
       </c>
       <c r="N10">
-        <v>397.2315256</v>
+        <v>393.9604663</v>
       </c>
       <c r="O10">
-        <v>79.44630512000001</v>
+        <v>78.79209326</v>
       </c>
       <c r="P10">
-        <v>317.78522048</v>
+        <v>315.16837304</v>
       </c>
       <c r="Q10">
-        <v>369.4852204800001</v>
+        <v>366.8683730400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09179125503093288</v>
+        <v>0.09220214804469981</v>
       </c>
       <c r="T10">
-        <v>0.9456286100706205</v>
+        <v>0.9540770029060588</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.17977393439489</v>
+        <v>14.38202127501769</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08752555472067683</v>
+        <v>0.08738395481289542</v>
       </c>
       <c r="C11">
-        <v>6037.940398305604</v>
+        <v>5993.535579483298</v>
       </c>
       <c r="D11">
-        <v>6411.219398305603</v>
+        <v>6431.845579483298</v>
       </c>
       <c r="E11">
-        <v>298.8789999999999</v>
+        <v>363.91</v>
       </c>
       <c r="F11">
-        <v>585.2789999999999</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="G11">
         <v>212</v>
@@ -2320,28 +2320,28 @@
         <v>423.4</v>
       </c>
       <c r="M11">
-        <v>29.43953369999999</v>
+        <v>32.710593</v>
       </c>
       <c r="N11">
-        <v>393.9604663</v>
+        <v>390.689407</v>
       </c>
       <c r="O11">
-        <v>78.79209326</v>
+        <v>78.1378814</v>
       </c>
       <c r="P11">
-        <v>315.16837304</v>
+        <v>312.5515256</v>
       </c>
       <c r="Q11">
-        <v>366.8683730400001</v>
+        <v>364.2515256</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09220214804469981</v>
+        <v>0.09262217201432824</v>
       </c>
       <c r="T11">
-        <v>0.9540770029060588</v>
+        <v>0.962713137804507</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.38202127501769</v>
+        <v>12.94381914751591</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08738395481289542</v>
+        <v>0.08724235490511399</v>
       </c>
       <c r="C12">
-        <v>5993.535579483298</v>
+        <v>5949.26390615642</v>
       </c>
       <c r="D12">
-        <v>6431.845579483298</v>
+        <v>6452.60490615642</v>
       </c>
       <c r="E12">
-        <v>363.91</v>
+        <v>428.9409999999999</v>
       </c>
       <c r="F12">
-        <v>650.3099999999999</v>
+        <v>715.3409999999999</v>
       </c>
       <c r="G12">
         <v>212</v>
@@ -2402,28 +2402,28 @@
         <v>423.4</v>
       </c>
       <c r="M12">
-        <v>32.710593</v>
+        <v>35.98165229999999</v>
       </c>
       <c r="N12">
-        <v>390.689407</v>
+        <v>387.4183477</v>
       </c>
       <c r="O12">
-        <v>78.1378814</v>
+        <v>77.48366953999999</v>
       </c>
       <c r="P12">
-        <v>312.5515256</v>
+        <v>309.93467816</v>
       </c>
       <c r="Q12">
-        <v>364.2515256</v>
+        <v>361.63467816</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09262217201432824</v>
+        <v>0.09305163472484718</v>
       </c>
       <c r="T12">
-        <v>0.9627131378045072</v>
+        <v>0.9715433431501113</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.94381914751591</v>
+        <v>11.76710831592356</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08724235490511399</v>
+        <v>0.08710075499733258</v>
       </c>
       <c r="C13">
-        <v>5949.26390615642</v>
+        <v>5905.126671714599</v>
       </c>
       <c r="D13">
-        <v>6452.60490615642</v>
+        <v>6473.498671714599</v>
       </c>
       <c r="E13">
-        <v>428.9409999999999</v>
+        <v>493.972</v>
       </c>
       <c r="F13">
-        <v>715.3409999999999</v>
+        <v>780.372</v>
       </c>
       <c r="G13">
         <v>212</v>
@@ -2484,28 +2484,28 @@
         <v>423.4</v>
       </c>
       <c r="M13">
-        <v>35.98165229999999</v>
+        <v>39.2527116</v>
       </c>
       <c r="N13">
-        <v>387.4183477</v>
+        <v>384.1472884</v>
       </c>
       <c r="O13">
-        <v>77.48366953999999</v>
+        <v>76.82945768</v>
       </c>
       <c r="P13">
-        <v>309.93467816</v>
+        <v>307.31783072</v>
       </c>
       <c r="Q13">
-        <v>361.63467816</v>
+        <v>359.01783072</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09305163472484718</v>
+        <v>0.09349085795151429</v>
       </c>
       <c r="T13">
-        <v>0.9715433431501113</v>
+        <v>0.9805742349808431</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.76710831592356</v>
+        <v>10.78651595626326</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08710075499733258</v>
+        <v>0.08695915508955115</v>
       </c>
       <c r="C14">
-        <v>5905.126671714599</v>
+        <v>5861.125186354061</v>
       </c>
       <c r="D14">
-        <v>6473.498671714599</v>
+        <v>6494.528186354061</v>
       </c>
       <c r="E14">
-        <v>493.972</v>
+        <v>559.0029999999999</v>
       </c>
       <c r="F14">
-        <v>780.372</v>
+        <v>845.4029999999999</v>
       </c>
       <c r="G14">
         <v>212</v>
@@ -2566,28 +2566,28 @@
         <v>423.4</v>
       </c>
       <c r="M14">
-        <v>39.2527116</v>
+        <v>42.5237709</v>
       </c>
       <c r="N14">
-        <v>384.1472884</v>
+        <v>380.8762291</v>
       </c>
       <c r="O14">
-        <v>76.82945768</v>
+        <v>76.17524582</v>
       </c>
       <c r="P14">
-        <v>307.31783072</v>
+        <v>304.70098328</v>
       </c>
       <c r="Q14">
-        <v>359.01783072</v>
+        <v>356.40098328</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09349085795151429</v>
+        <v>0.0939401782638519</v>
       </c>
       <c r="T14">
-        <v>0.9805742349808431</v>
+        <v>0.9898127335203271</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.78651595626326</v>
+        <v>9.956783959627627</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08695915508955115</v>
+        <v>0.08681755518176974</v>
       </c>
       <c r="C15">
-        <v>5861.125186354061</v>
+        <v>5817.260777351487</v>
       </c>
       <c r="D15">
-        <v>6494.528186354061</v>
+        <v>6515.694777351488</v>
       </c>
       <c r="E15">
-        <v>559.0029999999999</v>
+        <v>624.034</v>
       </c>
       <c r="F15">
-        <v>845.4029999999999</v>
+        <v>910.434</v>
       </c>
       <c r="G15">
         <v>212</v>
@@ -2648,28 +2648,28 @@
         <v>423.4</v>
       </c>
       <c r="M15">
-        <v>42.5237709</v>
+        <v>45.79483019999999</v>
       </c>
       <c r="N15">
-        <v>380.8762291</v>
+        <v>377.6051698</v>
       </c>
       <c r="O15">
-        <v>76.17524582</v>
+        <v>75.52103396</v>
       </c>
       <c r="P15">
-        <v>304.70098328</v>
+        <v>302.08413584</v>
       </c>
       <c r="Q15">
-        <v>356.40098328</v>
+        <v>353.78413584</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0939401782638519</v>
+        <v>0.09439994788577877</v>
       </c>
       <c r="T15">
-        <v>0.9898127335203271</v>
+        <v>0.999266080863055</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.956783959627627</v>
+        <v>9.245585105368511</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08681755518176974</v>
+        <v>0.0868559552739883</v>
       </c>
       <c r="C16">
-        <v>5817.260777351487</v>
+        <v>5746.476044886175</v>
       </c>
       <c r="D16">
-        <v>6515.694777351488</v>
+        <v>6509.941044886175</v>
       </c>
       <c r="E16">
-        <v>624.034</v>
+        <v>689.0650000000001</v>
       </c>
       <c r="F16">
-        <v>910.434</v>
+        <v>975.465</v>
       </c>
       <c r="G16">
         <v>212</v>
@@ -2730,45 +2730,45 @@
         <v>423.4</v>
       </c>
       <c r="M16">
-        <v>45.79483019999999</v>
+        <v>50.529087</v>
       </c>
       <c r="N16">
-        <v>377.6051698</v>
+        <v>372.870913</v>
       </c>
       <c r="O16">
-        <v>75.52103396</v>
+        <v>74.5741826</v>
       </c>
       <c r="P16">
-        <v>302.08413584</v>
+        <v>298.2967304</v>
       </c>
       <c r="Q16">
-        <v>353.78413584</v>
+        <v>349.9967304</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09439994788577877</v>
+        <v>0.09487053561645684</v>
       </c>
       <c r="T16">
-        <v>0.999266080863055</v>
+        <v>1.008941859907965</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.245585105368511</v>
+        <v>8.379332086487135</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0868559552739883</v>
+        <v>0.08672635536620689</v>
       </c>
       <c r="C17">
-        <v>5746.476044886175</v>
+        <v>5700.904679333149</v>
       </c>
       <c r="D17">
-        <v>6509.941044886175</v>
+        <v>6529.400679333149</v>
       </c>
       <c r="E17">
-        <v>689.0649999999999</v>
+        <v>754.0959999999999</v>
       </c>
       <c r="F17">
-        <v>975.4649999999999</v>
+        <v>1040.496</v>
       </c>
       <c r="G17">
         <v>212</v>
@@ -2812,28 +2812,28 @@
         <v>423.4</v>
       </c>
       <c r="M17">
-        <v>50.529087</v>
+        <v>53.89769279999999</v>
       </c>
       <c r="N17">
-        <v>372.870913</v>
+        <v>369.5023072</v>
       </c>
       <c r="O17">
-        <v>74.5741826</v>
+        <v>73.90046144</v>
       </c>
       <c r="P17">
-        <v>298.2967304</v>
+        <v>295.6018457599999</v>
       </c>
       <c r="Q17">
-        <v>349.9967304</v>
+        <v>347.30184576</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09487053561645684</v>
+        <v>0.09535232781691297</v>
       </c>
       <c r="T17">
-        <v>1.008941859907965</v>
+        <v>1.01884801464442</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.379332086487135</v>
+        <v>7.855623831081689</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08672635536620689</v>
+        <v>0.08659675545842548</v>
       </c>
       <c r="C18">
-        <v>5700.904679333149</v>
+        <v>5655.450000771075</v>
       </c>
       <c r="D18">
-        <v>6529.400679333149</v>
+        <v>6548.977000771075</v>
       </c>
       <c r="E18">
-        <v>754.0959999999999</v>
+        <v>819.1270000000001</v>
       </c>
       <c r="F18">
-        <v>1040.496</v>
+        <v>1105.527</v>
       </c>
       <c r="G18">
         <v>212</v>
@@ -2894,28 +2894,28 @@
         <v>423.4</v>
       </c>
       <c r="M18">
-        <v>53.89769279999999</v>
+        <v>57.2662986</v>
       </c>
       <c r="N18">
-        <v>369.5023072</v>
+        <v>366.1337013999999</v>
       </c>
       <c r="O18">
-        <v>73.90046144</v>
+        <v>73.22674027999999</v>
       </c>
       <c r="P18">
-        <v>295.6018457599999</v>
+        <v>292.9069611199999</v>
       </c>
       <c r="Q18">
-        <v>347.30184576</v>
+        <v>344.60696112</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09535232781691297</v>
+        <v>0.0958457294679825</v>
       </c>
       <c r="T18">
-        <v>1.01884801464442</v>
+        <v>1.028992871904645</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.855623831081689</v>
+        <v>7.393528311606295</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08659675545842548</v>
+        <v>0.08646715555064406</v>
       </c>
       <c r="C19">
-        <v>5655.450000771075</v>
+        <v>5610.113061902111</v>
       </c>
       <c r="D19">
-        <v>6548.977000771075</v>
+        <v>6568.671061902111</v>
       </c>
       <c r="E19">
-        <v>819.1270000000001</v>
+        <v>884.158</v>
       </c>
       <c r="F19">
-        <v>1105.527</v>
+        <v>1170.558</v>
       </c>
       <c r="G19">
         <v>212</v>
@@ -2976,28 +2976,28 @@
         <v>423.4</v>
       </c>
       <c r="M19">
-        <v>57.2662986</v>
+        <v>60.6349044</v>
       </c>
       <c r="N19">
-        <v>366.1337013999999</v>
+        <v>362.7650956</v>
       </c>
       <c r="O19">
-        <v>73.22674027999999</v>
+        <v>72.55301912</v>
       </c>
       <c r="P19">
-        <v>292.9069611199999</v>
+        <v>290.21207648</v>
       </c>
       <c r="Q19">
-        <v>344.60696112</v>
+        <v>341.9120764800001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0958457294679825</v>
+        <v>0.0963511653056635</v>
       </c>
       <c r="T19">
-        <v>1.028992871904645</v>
+        <v>1.039385164707803</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.393528311606295</v>
+        <v>6.98277673873928</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08646715555064406</v>
+        <v>0.08659595564286267</v>
       </c>
       <c r="C20">
-        <v>5610.113061902111</v>
+        <v>5525.509178951305</v>
       </c>
       <c r="D20">
-        <v>6568.671061902111</v>
+        <v>6549.098178951305</v>
       </c>
       <c r="E20">
-        <v>884.1579999999998</v>
+        <v>949.189</v>
       </c>
       <c r="F20">
-        <v>1170.558</v>
+        <v>1235.589</v>
       </c>
       <c r="G20">
         <v>212</v>
@@ -3058,45 +3058,45 @@
         <v>423.4</v>
       </c>
       <c r="M20">
-        <v>60.63490439999999</v>
+        <v>66.1040115</v>
       </c>
       <c r="N20">
-        <v>362.7650956</v>
+        <v>357.2959885</v>
       </c>
       <c r="O20">
-        <v>72.55301912</v>
+        <v>71.45919769999999</v>
       </c>
       <c r="P20">
-        <v>290.21207648</v>
+        <v>285.8367908</v>
       </c>
       <c r="Q20">
-        <v>341.9120764800001</v>
+        <v>337.5367908</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09635116530566348</v>
+        <v>0.09686908104057118</v>
       </c>
       <c r="T20">
-        <v>1.039385164707803</v>
+        <v>1.050034057333261</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.982776738739281</v>
+        <v>6.405057581112153</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08659595564286267</v>
+        <v>0.08647995573508122</v>
       </c>
       <c r="C21">
-        <v>5525.509178951305</v>
+        <v>5478.100669958665</v>
       </c>
       <c r="D21">
-        <v>6549.098178951305</v>
+        <v>6566.720669958665</v>
       </c>
       <c r="E21">
-        <v>949.189</v>
+        <v>1014.22</v>
       </c>
       <c r="F21">
-        <v>1235.589</v>
+        <v>1300.62</v>
       </c>
       <c r="G21">
         <v>212</v>
@@ -3140,28 +3140,28 @@
         <v>423.4</v>
       </c>
       <c r="M21">
-        <v>66.1040115</v>
+        <v>69.58317</v>
       </c>
       <c r="N21">
-        <v>357.2959885</v>
+        <v>353.81683</v>
       </c>
       <c r="O21">
-        <v>71.45919769999999</v>
+        <v>70.763366</v>
       </c>
       <c r="P21">
-        <v>285.8367908</v>
+        <v>283.053464</v>
       </c>
       <c r="Q21">
-        <v>337.5367908</v>
+        <v>334.753464</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09686908104057118</v>
+        <v>0.09739994466885152</v>
       </c>
       <c r="T21">
-        <v>1.050034057333261</v>
+        <v>1.060949172274355</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.405057581112153</v>
+        <v>6.084804702056546</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08647995573508122</v>
+        <v>0.0863639558272998</v>
       </c>
       <c r="C22">
-        <v>5478.100669958665</v>
+        <v>5430.787255001163</v>
       </c>
       <c r="D22">
-        <v>6566.720669958665</v>
+        <v>6584.438255001163</v>
       </c>
       <c r="E22">
-        <v>1014.22</v>
+        <v>1079.251</v>
       </c>
       <c r="F22">
-        <v>1300.62</v>
+        <v>1365.651</v>
       </c>
       <c r="G22">
         <v>212</v>
@@ -3222,28 +3222,28 @@
         <v>423.4</v>
       </c>
       <c r="M22">
-        <v>69.58317</v>
+        <v>73.06232850000001</v>
       </c>
       <c r="N22">
-        <v>353.81683</v>
+        <v>350.3376714999999</v>
       </c>
       <c r="O22">
-        <v>70.763366</v>
+        <v>70.06753429999999</v>
       </c>
       <c r="P22">
-        <v>283.053464</v>
+        <v>280.2701372</v>
       </c>
       <c r="Q22">
-        <v>334.753464</v>
+        <v>331.9701372</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09739994466885152</v>
+        <v>0.09794424788265799</v>
       </c>
       <c r="T22">
-        <v>1.060949172274355</v>
+        <v>1.072140619239274</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.084804702056546</v>
+        <v>5.795052097196709</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0863639558272998</v>
+        <v>0.08638875591951839</v>
       </c>
       <c r="C23">
-        <v>5430.787255001163</v>
+        <v>5361.960309922945</v>
       </c>
       <c r="D23">
-        <v>6584.438255001163</v>
+        <v>6580.642309922945</v>
       </c>
       <c r="E23">
-        <v>1079.251</v>
+        <v>1144.282</v>
       </c>
       <c r="F23">
-        <v>1365.651</v>
+        <v>1430.682</v>
       </c>
       <c r="G23">
         <v>212</v>
@@ -3304,45 +3304,45 @@
         <v>423.4</v>
       </c>
       <c r="M23">
-        <v>73.06232849999999</v>
+        <v>77.68603259999999</v>
       </c>
       <c r="N23">
-        <v>350.3376715</v>
+        <v>345.7139674</v>
       </c>
       <c r="O23">
-        <v>70.06753430000001</v>
+        <v>69.14279348000001</v>
       </c>
       <c r="P23">
-        <v>280.2701372</v>
+        <v>276.57117392</v>
       </c>
       <c r="Q23">
-        <v>331.9701372000001</v>
+        <v>328.27117392</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09794424788265799</v>
+        <v>0.09850250758912614</v>
       </c>
       <c r="T23">
-        <v>1.072140619239274</v>
+        <v>1.083619026382781</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.795052097196711</v>
+        <v>5.450143170266621</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08638875591951839</v>
+        <v>0.08627915601173697</v>
       </c>
       <c r="C24">
-        <v>5361.960309922945</v>
+        <v>5313.738015033496</v>
       </c>
       <c r="D24">
-        <v>6580.642309922945</v>
+        <v>6597.451015033495</v>
       </c>
       <c r="E24">
-        <v>1144.282</v>
+        <v>1209.313</v>
       </c>
       <c r="F24">
-        <v>1430.682</v>
+        <v>1495.713</v>
       </c>
       <c r="G24">
         <v>212</v>
@@ -3386,28 +3386,28 @@
         <v>423.4</v>
       </c>
       <c r="M24">
-        <v>77.68603259999999</v>
+        <v>81.2172159</v>
       </c>
       <c r="N24">
-        <v>345.7139674</v>
+        <v>342.1827841</v>
       </c>
       <c r="O24">
-        <v>69.14279348000001</v>
+        <v>68.43655682000001</v>
       </c>
       <c r="P24">
-        <v>276.57117392</v>
+        <v>273.74622728</v>
       </c>
       <c r="Q24">
-        <v>328.27117392</v>
+        <v>325.44622728</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09850250758912614</v>
+        <v>0.09907526754771034</v>
       </c>
       <c r="T24">
-        <v>1.083619026382781</v>
+        <v>1.095395573971574</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.450143170266621</v>
+        <v>5.213180423733289</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08627915601173697</v>
+        <v>0.08616955610395556</v>
       </c>
       <c r="C25">
-        <v>5313.738015033496</v>
+        <v>5265.60180781308</v>
       </c>
       <c r="D25">
-        <v>6597.451015033495</v>
+        <v>6614.34580781308</v>
       </c>
       <c r="E25">
-        <v>1209.313</v>
+        <v>1274.344</v>
       </c>
       <c r="F25">
-        <v>1495.713</v>
+        <v>1560.744</v>
       </c>
       <c r="G25">
         <v>212</v>
@@ -3468,28 +3468,28 @@
         <v>423.4</v>
       </c>
       <c r="M25">
-        <v>81.2172159</v>
+        <v>84.74839919999999</v>
       </c>
       <c r="N25">
-        <v>342.1827841</v>
+        <v>338.6516008</v>
       </c>
       <c r="O25">
-        <v>68.43655682000001</v>
+        <v>67.73032016000001</v>
       </c>
       <c r="P25">
-        <v>273.74622728</v>
+        <v>270.92128064</v>
       </c>
       <c r="Q25">
-        <v>325.44622728</v>
+        <v>322.62128064</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09907526754771034</v>
+        <v>0.09966310013678362</v>
       </c>
       <c r="T25">
-        <v>1.095395573971574</v>
+        <v>1.10748203070744</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.213180423733289</v>
+        <v>4.995964572744402</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08616955610395556</v>
+        <v>0.08605995619617413</v>
       </c>
       <c r="C26">
-        <v>5265.60180781308</v>
+        <v>5217.552351321155</v>
       </c>
       <c r="D26">
-        <v>6614.34580781308</v>
+        <v>6631.327351321154</v>
       </c>
       <c r="E26">
-        <v>1274.344</v>
+        <v>1339.375</v>
       </c>
       <c r="F26">
-        <v>1560.744</v>
+        <v>1625.775</v>
       </c>
       <c r="G26">
         <v>212</v>
@@ -3550,28 +3550,28 @@
         <v>423.4</v>
       </c>
       <c r="M26">
-        <v>84.74839919999999</v>
+        <v>88.27958249999999</v>
       </c>
       <c r="N26">
-        <v>338.6516008</v>
+        <v>335.1204175</v>
       </c>
       <c r="O26">
-        <v>67.73032016000001</v>
+        <v>67.0240835</v>
       </c>
       <c r="P26">
-        <v>270.92128064</v>
+        <v>268.096334</v>
       </c>
       <c r="Q26">
-        <v>322.62128064</v>
+        <v>319.796334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09966310013678362</v>
+        <v>0.1002666082615655</v>
       </c>
       <c r="T26">
-        <v>1.10748203070744</v>
+        <v>1.119890792956263</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.995964572744402</v>
+        <v>4.796125989834626</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08605995619617413</v>
+        <v>0.08595035628839272</v>
       </c>
       <c r="C27">
-        <v>5217.552351321155</v>
+        <v>5169.590315443994</v>
       </c>
       <c r="D27">
-        <v>6631.327351321154</v>
+        <v>6648.396315443993</v>
       </c>
       <c r="E27">
-        <v>1339.375</v>
+        <v>1404.406</v>
       </c>
       <c r="F27">
-        <v>1625.775</v>
+        <v>1690.806</v>
       </c>
       <c r="G27">
         <v>212</v>
@@ -3632,28 +3632,28 @@
         <v>423.4</v>
       </c>
       <c r="M27">
-        <v>88.27958249999999</v>
+        <v>91.8107658</v>
       </c>
       <c r="N27">
-        <v>335.1204175</v>
+        <v>331.5892342</v>
       </c>
       <c r="O27">
-        <v>67.0240835</v>
+        <v>66.31784684</v>
       </c>
       <c r="P27">
-        <v>268.096334</v>
+        <v>265.2713873599999</v>
       </c>
       <c r="Q27">
-        <v>319.796334</v>
+        <v>316.97138736</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1002666082615655</v>
+        <v>0.1008864274167469</v>
       </c>
       <c r="T27">
-        <v>1.119890792956263</v>
+        <v>1.132634927157757</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.796125989834626</v>
+        <v>4.611659605610217</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08595035628839272</v>
+        <v>0.08584075638061128</v>
       </c>
       <c r="C28">
-        <v>5169.590315443994</v>
+        <v>5121.716376982806</v>
       </c>
       <c r="D28">
-        <v>6648.396315443993</v>
+        <v>6665.553376982805</v>
       </c>
       <c r="E28">
-        <v>1404.406</v>
+        <v>1469.437</v>
       </c>
       <c r="F28">
-        <v>1690.806</v>
+        <v>1755.837</v>
       </c>
       <c r="G28">
         <v>212</v>
@@ -3714,28 +3714,28 @@
         <v>423.4</v>
       </c>
       <c r="M28">
-        <v>91.8107658</v>
+        <v>95.34194910000001</v>
       </c>
       <c r="N28">
-        <v>331.5892342</v>
+        <v>328.0580509</v>
       </c>
       <c r="O28">
-        <v>66.31784684</v>
+        <v>65.61161018</v>
       </c>
       <c r="P28">
-        <v>265.2713873599999</v>
+        <v>262.4464407199999</v>
       </c>
       <c r="Q28">
-        <v>316.97138736</v>
+        <v>314.14644072</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1008864274167469</v>
+        <v>0.1015232279186456</v>
       </c>
       <c r="T28">
-        <v>1.132634927157757</v>
+        <v>1.145728215720936</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.611659605610217</v>
+        <v>4.440857397995023</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08584075638061128</v>
+        <v>0.08573115647282986</v>
       </c>
       <c r="C29">
-        <v>5121.716376982806</v>
+        <v>5073.931219743155</v>
       </c>
       <c r="D29">
-        <v>6665.553376982805</v>
+        <v>6682.799219743155</v>
       </c>
       <c r="E29">
-        <v>1469.437</v>
+        <v>1534.468</v>
       </c>
       <c r="F29">
-        <v>1755.837</v>
+        <v>1820.868</v>
       </c>
       <c r="G29">
         <v>212</v>
@@ -3796,28 +3796,28 @@
         <v>423.4</v>
       </c>
       <c r="M29">
-        <v>95.34194910000001</v>
+        <v>98.8731324</v>
       </c>
       <c r="N29">
-        <v>328.0580509</v>
+        <v>324.5268675999999</v>
       </c>
       <c r="O29">
-        <v>65.61161018</v>
+        <v>64.90537352</v>
       </c>
       <c r="P29">
-        <v>262.4464407199999</v>
+        <v>259.6214940799999</v>
       </c>
       <c r="Q29">
-        <v>314.14644072</v>
+        <v>311.32149408</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1015232279186456</v>
+        <v>0.1021777173233748</v>
       </c>
       <c r="T29">
-        <v>1.145728215720936</v>
+        <v>1.159185206744202</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.440857397995023</v>
+        <v>4.282255348066629</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08573115647282986</v>
+        <v>0.08585355656504844</v>
       </c>
       <c r="C30">
-        <v>5073.931219743155</v>
+        <v>4989.64603630454</v>
       </c>
       <c r="D30">
-        <v>6682.799219743155</v>
+        <v>6663.54503630454</v>
       </c>
       <c r="E30">
-        <v>1534.468</v>
+        <v>1599.499</v>
       </c>
       <c r="F30">
-        <v>1820.868</v>
+        <v>1885.899</v>
       </c>
       <c r="G30">
         <v>212</v>
@@ -3878,45 +3878,45 @@
         <v>423.4</v>
       </c>
       <c r="M30">
-        <v>98.8731324</v>
+        <v>104.2902147</v>
       </c>
       <c r="N30">
-        <v>324.5268675999999</v>
+        <v>319.1097853</v>
       </c>
       <c r="O30">
-        <v>64.90537352</v>
+        <v>63.82195706</v>
       </c>
       <c r="P30">
-        <v>259.6214940799999</v>
+        <v>255.28782824</v>
       </c>
       <c r="Q30">
-        <v>311.32149408</v>
+        <v>306.9878282400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1021777173233748</v>
+        <v>0.102850643049364</v>
       </c>
       <c r="T30">
-        <v>1.159185206744202</v>
+        <v>1.173021267937139</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.282255348066629</v>
+        <v>4.059824799651121</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08585355656504844</v>
+        <v>0.08575195665726704</v>
       </c>
       <c r="C31">
-        <v>4989.646036304541</v>
+        <v>4940.589396614911</v>
       </c>
       <c r="D31">
-        <v>6663.54503630454</v>
+        <v>6679.519396614911</v>
       </c>
       <c r="E31">
-        <v>1599.499</v>
+        <v>1664.53</v>
       </c>
       <c r="F31">
-        <v>1885.899</v>
+        <v>1950.93</v>
       </c>
       <c r="G31">
         <v>212</v>
@@ -3960,28 +3960,28 @@
         <v>423.4</v>
       </c>
       <c r="M31">
-        <v>104.2902147</v>
+        <v>107.886429</v>
       </c>
       <c r="N31">
-        <v>319.1097853</v>
+        <v>315.513571</v>
       </c>
       <c r="O31">
-        <v>63.82195706</v>
+        <v>63.10271419999999</v>
       </c>
       <c r="P31">
-        <v>255.28782824</v>
+        <v>252.4108568</v>
       </c>
       <c r="Q31">
-        <v>306.9878282400001</v>
+        <v>304.1108568</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.102850643049364</v>
+        <v>0.1035427952246672</v>
       </c>
       <c r="T31">
-        <v>1.173021267937139</v>
+        <v>1.187252645164159</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.059824799651123</v>
+        <v>3.924497306329418</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08575195665726704</v>
+        <v>0.0856503567494856</v>
       </c>
       <c r="C32">
-        <v>4940.589396614911</v>
+        <v>4891.609530892729</v>
       </c>
       <c r="D32">
-        <v>6679.519396614911</v>
+        <v>6695.570530892729</v>
       </c>
       <c r="E32">
-        <v>1664.53</v>
+        <v>1729.561</v>
       </c>
       <c r="F32">
-        <v>1950.93</v>
+        <v>2015.961</v>
       </c>
       <c r="G32">
         <v>212</v>
@@ -4042,28 +4042,28 @@
         <v>423.4</v>
       </c>
       <c r="M32">
-        <v>107.886429</v>
+        <v>111.4826433</v>
       </c>
       <c r="N32">
-        <v>315.513571</v>
+        <v>311.9173567</v>
       </c>
       <c r="O32">
-        <v>63.10271419999999</v>
+        <v>62.38347134</v>
       </c>
       <c r="P32">
-        <v>252.4108568</v>
+        <v>249.53388536</v>
       </c>
       <c r="Q32">
-        <v>304.1108568</v>
+        <v>301.23388536</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1035427952246672</v>
+        <v>0.1042550097818632</v>
       </c>
       <c r="T32">
-        <v>1.187252645164159</v>
+        <v>1.201896526078919</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.924497306329418</v>
+        <v>3.797900619028469</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0856503567494856</v>
+        <v>0.08554875684170417</v>
       </c>
       <c r="C33">
-        <v>4891.609530892729</v>
+        <v>4842.70699394333</v>
       </c>
       <c r="D33">
-        <v>6695.570530892729</v>
+        <v>6711.698993943329</v>
       </c>
       <c r="E33">
-        <v>1729.561</v>
+        <v>1794.592</v>
       </c>
       <c r="F33">
-        <v>2015.961</v>
+        <v>2080.992</v>
       </c>
       <c r="G33">
         <v>212</v>
@@ -4124,28 +4124,28 @@
         <v>423.4</v>
       </c>
       <c r="M33">
-        <v>111.4826433</v>
+        <v>115.0788576</v>
       </c>
       <c r="N33">
-        <v>311.9173567</v>
+        <v>308.3211424</v>
       </c>
       <c r="O33">
-        <v>62.38347134</v>
+        <v>61.66422848</v>
       </c>
       <c r="P33">
-        <v>249.53388536</v>
+        <v>246.65691392</v>
       </c>
       <c r="Q33">
-        <v>301.23388536</v>
+        <v>298.35691392</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1042550097818632</v>
+        <v>0.1049881718260356</v>
       </c>
       <c r="T33">
-        <v>1.201896526078919</v>
+        <v>1.216971109373524</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.797900619028469</v>
+        <v>3.67921622468383</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08554875684170417</v>
+        <v>0.08544715693392277</v>
       </c>
       <c r="C34">
-        <v>4842.70699394333</v>
+        <v>4793.882345930675</v>
       </c>
       <c r="D34">
-        <v>6711.698993943329</v>
+        <v>6727.905345930675</v>
       </c>
       <c r="E34">
-        <v>1794.592</v>
+        <v>1859.623</v>
       </c>
       <c r="F34">
-        <v>2080.992</v>
+        <v>2146.023</v>
       </c>
       <c r="G34">
         <v>212</v>
@@ -4206,28 +4206,28 @@
         <v>423.4</v>
       </c>
       <c r="M34">
-        <v>115.0788576</v>
+        <v>118.6750719</v>
       </c>
       <c r="N34">
-        <v>308.3211424</v>
+        <v>304.7249280999999</v>
       </c>
       <c r="O34">
-        <v>61.66422848</v>
+        <v>60.94498561999999</v>
       </c>
       <c r="P34">
-        <v>246.65691392</v>
+        <v>243.77994248</v>
       </c>
       <c r="Q34">
-        <v>298.35691392</v>
+        <v>295.47994248</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1049881718260356</v>
+        <v>0.1057432193043623</v>
       </c>
       <c r="T34">
-        <v>1.216971109373524</v>
+        <v>1.232495680229163</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.67921622468383</v>
+        <v>3.567724823935834</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08544715693392277</v>
+        <v>0.08534555702614134</v>
       </c>
       <c r="C35">
-        <v>4793.882345930675</v>
+        <v>4745.13615244222</v>
       </c>
       <c r="D35">
-        <v>6727.905345930675</v>
+        <v>6744.19015244222</v>
       </c>
       <c r="E35">
-        <v>1859.623</v>
+        <v>1924.654</v>
       </c>
       <c r="F35">
-        <v>2146.023</v>
+        <v>2211.054</v>
       </c>
       <c r="G35">
         <v>212</v>
@@ -4288,28 +4288,28 @@
         <v>423.4</v>
       </c>
       <c r="M35">
-        <v>118.6750719</v>
+        <v>122.2712862</v>
       </c>
       <c r="N35">
-        <v>304.7249280999999</v>
+        <v>301.1287138</v>
       </c>
       <c r="O35">
-        <v>60.94498561999999</v>
+        <v>60.22574276</v>
       </c>
       <c r="P35">
-        <v>243.77994248</v>
+        <v>240.90297104</v>
       </c>
       <c r="Q35">
-        <v>295.47994248</v>
+        <v>292.60297104</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1057432193043623</v>
+        <v>0.1065211470093051</v>
       </c>
       <c r="T35">
-        <v>1.232495680229163</v>
+        <v>1.248490692625882</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.567724823935834</v>
+        <v>3.462791740878898</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08534555702614134</v>
+        <v>0.08524395711835993</v>
       </c>
       <c r="C36">
-        <v>4745.13615244222</v>
+        <v>4696.468984554677</v>
       </c>
       <c r="D36">
-        <v>6744.19015244222</v>
+        <v>6760.553984554677</v>
       </c>
       <c r="E36">
-        <v>1924.654</v>
+        <v>1989.685</v>
       </c>
       <c r="F36">
-        <v>2211.054</v>
+        <v>2276.085</v>
       </c>
       <c r="G36">
         <v>212</v>
@@ -4370,28 +4370,28 @@
         <v>423.4</v>
       </c>
       <c r="M36">
-        <v>122.2712862</v>
+        <v>125.8675005</v>
       </c>
       <c r="N36">
-        <v>301.1287138</v>
+        <v>297.5324995</v>
       </c>
       <c r="O36">
-        <v>60.22574276</v>
+        <v>59.50649989999999</v>
       </c>
       <c r="P36">
-        <v>240.90297104</v>
+        <v>238.0259996</v>
       </c>
       <c r="Q36">
-        <v>292.60297104</v>
+        <v>289.7259996</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1065211470093051</v>
+        <v>0.107323010951323</v>
       </c>
       <c r="T36">
-        <v>1.248490692625882</v>
+        <v>1.264977859250192</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.462791740878898</v>
+        <v>3.363854833996644</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08524395711835993</v>
+        <v>0.08514235721057851</v>
       </c>
       <c r="C37">
-        <v>4696.468984554677</v>
+        <v>4647.881418900802</v>
       </c>
       <c r="D37">
-        <v>6760.553984554677</v>
+        <v>6776.997418900802</v>
       </c>
       <c r="E37">
-        <v>1989.685</v>
+        <v>2054.716</v>
       </c>
       <c r="F37">
-        <v>2276.085</v>
+        <v>2341.116</v>
       </c>
       <c r="G37">
         <v>212</v>
@@ -4452,28 +4452,28 @@
         <v>423.4</v>
       </c>
       <c r="M37">
-        <v>125.8675005</v>
+        <v>129.4637148</v>
       </c>
       <c r="N37">
-        <v>297.5324995</v>
+        <v>293.9362852</v>
       </c>
       <c r="O37">
-        <v>59.50649989999999</v>
+        <v>58.78725704</v>
       </c>
       <c r="P37">
-        <v>238.0259996</v>
+        <v>235.14902816</v>
       </c>
       <c r="Q37">
-        <v>289.7259996</v>
+        <v>286.84902816</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.107323010951323</v>
+        <v>0.1081499331415289</v>
       </c>
       <c r="T37">
-        <v>1.264977859250192</v>
+        <v>1.281980249831512</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.363854833996644</v>
+        <v>3.270414421941182</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08514235721057853</v>
+        <v>0.0850407573027971</v>
       </c>
       <c r="C38">
-        <v>4647.881418900799</v>
+        <v>4599.374037737104</v>
       </c>
       <c r="D38">
-        <v>6776.997418900799</v>
+        <v>6793.521037737104</v>
       </c>
       <c r="E38">
-        <v>2054.715999999999</v>
+        <v>2119.747</v>
       </c>
       <c r="F38">
-        <v>2341.116</v>
+        <v>2406.147</v>
       </c>
       <c r="G38">
         <v>212</v>
@@ -4534,28 +4534,28 @@
         <v>423.4</v>
       </c>
       <c r="M38">
-        <v>129.4637148</v>
+        <v>133.0599291</v>
       </c>
       <c r="N38">
-        <v>293.9362852</v>
+        <v>290.3400709</v>
       </c>
       <c r="O38">
-        <v>58.78725704</v>
+        <v>58.06801418000001</v>
       </c>
       <c r="P38">
-        <v>235.14902816</v>
+        <v>232.27205672</v>
       </c>
       <c r="Q38">
-        <v>286.84902816</v>
+        <v>283.9720567200001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081499331415289</v>
+        <v>0.1090031068298367</v>
       </c>
       <c r="T38">
-        <v>1.281980249831512</v>
+        <v>1.299522398843985</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.270414421941182</v>
+        <v>3.182024842969798</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0850407573027971</v>
+        <v>0.08493915739501567</v>
       </c>
       <c r="C39">
-        <v>4599.374037737104</v>
+        <v>4550.947429012598</v>
       </c>
       <c r="D39">
-        <v>6793.521037737104</v>
+        <v>6810.125429012598</v>
       </c>
       <c r="E39">
-        <v>2119.747</v>
+        <v>2184.778</v>
       </c>
       <c r="F39">
-        <v>2406.147</v>
+        <v>2471.178</v>
       </c>
       <c r="G39">
         <v>212</v>
@@ -4616,28 +4616,28 @@
         <v>423.4</v>
       </c>
       <c r="M39">
-        <v>133.0599291</v>
+        <v>136.6561434</v>
       </c>
       <c r="N39">
-        <v>290.3400709</v>
+        <v>286.7438566</v>
       </c>
       <c r="O39">
-        <v>58.06801418000001</v>
+        <v>57.34877132</v>
       </c>
       <c r="P39">
-        <v>232.27205672</v>
+        <v>229.39508528</v>
       </c>
       <c r="Q39">
-        <v>283.9720567200001</v>
+        <v>281.09508528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1090031068298367</v>
+        <v>0.1098838022500253</v>
       </c>
       <c r="T39">
-        <v>1.299522398843985</v>
+        <v>1.317630423631053</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.182024842969798</v>
+        <v>3.098287347102172</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08493915739501567</v>
+        <v>0.08483755748723426</v>
       </c>
       <c r="C40">
-        <v>4550.947429012598</v>
+        <v>4502.602186438511</v>
       </c>
       <c r="D40">
-        <v>6810.125429012598</v>
+        <v>6826.811186438511</v>
       </c>
       <c r="E40">
-        <v>2184.778</v>
+        <v>2249.809</v>
       </c>
       <c r="F40">
-        <v>2471.178</v>
+        <v>2536.209</v>
       </c>
       <c r="G40">
         <v>212</v>
@@ -4698,28 +4698,28 @@
         <v>423.4</v>
       </c>
       <c r="M40">
-        <v>136.6561434</v>
+        <v>140.2523577</v>
       </c>
       <c r="N40">
-        <v>286.7438566</v>
+        <v>283.1476423</v>
       </c>
       <c r="O40">
-        <v>57.34877132</v>
+        <v>56.62952846</v>
       </c>
       <c r="P40">
-        <v>229.39508528</v>
+        <v>226.51811384</v>
       </c>
       <c r="Q40">
-        <v>281.09508528</v>
+        <v>278.21811384</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1098838022500253</v>
+        <v>0.1107933729298922</v>
       </c>
       <c r="T40">
-        <v>1.317630423631053</v>
+        <v>1.336332154148846</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.098287347102172</v>
+        <v>3.01884408179186</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08483755748723426</v>
+        <v>0.08553595757945283</v>
       </c>
       <c r="C41">
-        <v>4502.602186438511</v>
+        <v>4324.496323561812</v>
       </c>
       <c r="D41">
-        <v>6826.811186438511</v>
+        <v>6713.736323561811</v>
       </c>
       <c r="E41">
-        <v>2249.809</v>
+        <v>2314.84</v>
       </c>
       <c r="F41">
-        <v>2536.209</v>
+        <v>2601.24</v>
       </c>
       <c r="G41">
         <v>212</v>
@@ -4780,45 +4780,45 @@
         <v>423.4</v>
       </c>
       <c r="M41">
-        <v>140.2523577</v>
+        <v>150.351672</v>
       </c>
       <c r="N41">
-        <v>283.1476423</v>
+        <v>273.048328</v>
       </c>
       <c r="O41">
-        <v>56.62952846</v>
+        <v>54.6096656</v>
       </c>
       <c r="P41">
-        <v>226.51811384</v>
+        <v>218.4386624</v>
       </c>
       <c r="Q41">
-        <v>278.21811384</v>
+        <v>270.1386624</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1107933729298922</v>
+        <v>0.1117332626324214</v>
       </c>
       <c r="T41">
-        <v>1.336332154148846</v>
+        <v>1.355657275683898</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.01884408179186</v>
+        <v>2.81606445986181</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08553595757945283</v>
+        <v>0.08545435767167142</v>
       </c>
       <c r="C42">
-        <v>4324.496323561812</v>
+        <v>4272.483169118572</v>
       </c>
       <c r="D42">
-        <v>6713.736323561811</v>
+        <v>6726.754169118572</v>
       </c>
       <c r="E42">
-        <v>2314.84</v>
+        <v>2379.871</v>
       </c>
       <c r="F42">
-        <v>2601.24</v>
+        <v>2666.271</v>
       </c>
       <c r="G42">
         <v>212</v>
@@ -4862,28 +4862,28 @@
         <v>423.4</v>
       </c>
       <c r="M42">
-        <v>150.351672</v>
+        <v>154.1104638</v>
       </c>
       <c r="N42">
-        <v>273.048328</v>
+        <v>269.2895361999999</v>
       </c>
       <c r="O42">
-        <v>54.6096656</v>
+        <v>53.85790723999999</v>
       </c>
       <c r="P42">
-        <v>218.4386624</v>
+        <v>215.43162896</v>
       </c>
       <c r="Q42">
-        <v>270.1386624</v>
+        <v>267.13162896</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1117332626324214</v>
+        <v>0.1127050130028329</v>
       </c>
       <c r="T42">
-        <v>1.355657275683898</v>
+        <v>1.375637486084545</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.81606445986181</v>
+        <v>2.74737996084079</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08545435767167142</v>
+        <v>0.08537275776389001</v>
       </c>
       <c r="C43">
-        <v>4272.483169118572</v>
+        <v>4220.520595610345</v>
       </c>
       <c r="D43">
-        <v>6726.754169118572</v>
+        <v>6739.822595610346</v>
       </c>
       <c r="E43">
-        <v>2379.871</v>
+        <v>2444.902</v>
       </c>
       <c r="F43">
-        <v>2666.271</v>
+        <v>2731.302</v>
       </c>
       <c r="G43">
         <v>212</v>
@@ -4944,28 +4944,28 @@
         <v>423.4</v>
       </c>
       <c r="M43">
-        <v>154.1104638</v>
+        <v>157.8692556</v>
       </c>
       <c r="N43">
-        <v>269.2895361999999</v>
+        <v>265.5307443999999</v>
       </c>
       <c r="O43">
-        <v>53.85790723999999</v>
+        <v>53.10614887999999</v>
       </c>
       <c r="P43">
-        <v>215.43162896</v>
+        <v>212.42459552</v>
       </c>
       <c r="Q43">
-        <v>267.13162896</v>
+        <v>264.12459552</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1127050130028329</v>
+        <v>0.1137102720067069</v>
       </c>
       <c r="T43">
-        <v>1.375637486084545</v>
+        <v>1.396306669257628</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.74737996084079</v>
+        <v>2.681966152249342</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08537275776389</v>
+        <v>0.08529115785610858</v>
       </c>
       <c r="C44">
-        <v>4220.520595610347</v>
+        <v>4168.608898409869</v>
       </c>
       <c r="D44">
-        <v>6739.822595610347</v>
+        <v>6752.941898409868</v>
       </c>
       <c r="E44">
-        <v>2444.902</v>
+        <v>2509.933</v>
       </c>
       <c r="F44">
-        <v>2731.302</v>
+        <v>2796.333</v>
       </c>
       <c r="G44">
         <v>212</v>
@@ -5026,28 +5026,28 @@
         <v>423.4</v>
       </c>
       <c r="M44">
-        <v>157.8692556</v>
+        <v>161.6280474</v>
       </c>
       <c r="N44">
-        <v>265.5307444</v>
+        <v>261.7719526</v>
       </c>
       <c r="O44">
-        <v>53.10614888000001</v>
+        <v>52.35439052</v>
       </c>
       <c r="P44">
-        <v>212.42459552</v>
+        <v>209.41756208</v>
       </c>
       <c r="Q44">
-        <v>264.1245955200001</v>
+        <v>261.11756208</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1137102720067069</v>
+        <v>0.1147508032563308</v>
       </c>
       <c r="T44">
-        <v>1.396306669257628</v>
+        <v>1.417701086928012</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.681966152249343</v>
+        <v>2.619594846383079</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08529115785610858</v>
+        <v>0.08520955794832717</v>
       </c>
       <c r="C45">
-        <v>4168.608898409869</v>
+        <v>4116.748375194161</v>
       </c>
       <c r="D45">
-        <v>6752.941898409868</v>
+        <v>6766.11237519416</v>
       </c>
       <c r="E45">
-        <v>2509.933</v>
+        <v>2574.963999999999</v>
       </c>
       <c r="F45">
-        <v>2796.333</v>
+        <v>2861.364</v>
       </c>
       <c r="G45">
         <v>212</v>
@@ -5108,28 +5108,28 @@
         <v>423.4</v>
       </c>
       <c r="M45">
-        <v>161.6280474</v>
+        <v>165.3868392</v>
       </c>
       <c r="N45">
-        <v>261.7719526</v>
+        <v>258.0131608</v>
       </c>
       <c r="O45">
-        <v>52.35439052</v>
+        <v>51.60263216</v>
       </c>
       <c r="P45">
-        <v>209.41756208</v>
+        <v>206.41052864</v>
       </c>
       <c r="Q45">
-        <v>261.11756208</v>
+        <v>258.11052864</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1147508032563308</v>
+        <v>0.1158284963362985</v>
       </c>
       <c r="T45">
-        <v>1.417701086928012</v>
+        <v>1.439859590943767</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.619594846383079</v>
+        <v>2.560058599874373</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08520955794832717</v>
+        <v>0.08512795804054575</v>
       </c>
       <c r="C46">
-        <v>4116.748375194161</v>
+        <v>4064.939325967076</v>
       </c>
       <c r="D46">
-        <v>6766.11237519416</v>
+        <v>6779.334325967076</v>
       </c>
       <c r="E46">
-        <v>2574.963999999999</v>
+        <v>2639.995</v>
       </c>
       <c r="F46">
-        <v>2861.364</v>
+        <v>2926.395</v>
       </c>
       <c r="G46">
         <v>212</v>
@@ -5190,28 +5190,28 @@
         <v>423.4</v>
       </c>
       <c r="M46">
-        <v>165.3868392</v>
+        <v>169.145631</v>
       </c>
       <c r="N46">
-        <v>258.0131608</v>
+        <v>254.254369</v>
       </c>
       <c r="O46">
-        <v>51.60263216</v>
+        <v>50.8508738</v>
       </c>
       <c r="P46">
-        <v>206.41052864</v>
+        <v>203.4034952</v>
       </c>
       <c r="Q46">
-        <v>258.11052864</v>
+        <v>255.1034952</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1158284963362985</v>
+        <v>0.1169453782555377</v>
       </c>
       <c r="T46">
-        <v>1.439859590943767</v>
+        <v>1.462823858741913</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.560058599874373</v>
+        <v>2.503168408766053</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08512795804054575</v>
+        <v>0.08633435813276434</v>
       </c>
       <c r="C47">
-        <v>4064.939325967076</v>
+        <v>3809.548265322257</v>
       </c>
       <c r="D47">
-        <v>6779.334325967076</v>
+        <v>6588.974265322257</v>
       </c>
       <c r="E47">
-        <v>2639.995</v>
+        <v>2705.026</v>
       </c>
       <c r="F47">
-        <v>2926.395</v>
+        <v>2991.426</v>
       </c>
       <c r="G47">
         <v>212</v>
@@ -5272,45 +5272,45 @@
         <v>423.4</v>
       </c>
       <c r="M47">
-        <v>169.145631</v>
+        <v>183.3744138</v>
       </c>
       <c r="N47">
-        <v>254.254369</v>
+        <v>240.0255862</v>
       </c>
       <c r="O47">
-        <v>50.8508738</v>
+        <v>48.00511724</v>
       </c>
       <c r="P47">
-        <v>203.4034952</v>
+        <v>192.02046896</v>
       </c>
       <c r="Q47">
-        <v>255.1034952</v>
+        <v>243.72046896</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1169453782555377</v>
+        <v>0.1181036261717858</v>
       </c>
       <c r="T47">
-        <v>1.462823858741913</v>
+        <v>1.486638654977028</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.2</v>
       </c>
       <c r="W47">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.503168408766053</v>
+        <v>2.308937169728528</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08633435813276434</v>
+        <v>0.08628075822498291</v>
       </c>
       <c r="C48">
-        <v>3809.548265322257</v>
+        <v>3752.747674396681</v>
       </c>
       <c r="D48">
-        <v>6588.974265322257</v>
+        <v>6597.204674396681</v>
       </c>
       <c r="E48">
-        <v>2705.026</v>
+        <v>2770.057</v>
       </c>
       <c r="F48">
-        <v>2991.426</v>
+        <v>3056.457</v>
       </c>
       <c r="G48">
         <v>212</v>
@@ -5354,28 +5354,28 @@
         <v>423.4</v>
       </c>
       <c r="M48">
-        <v>183.3744138</v>
+        <v>187.3608141</v>
       </c>
       <c r="N48">
-        <v>240.0255862</v>
+        <v>236.0391859</v>
       </c>
       <c r="O48">
-        <v>48.00511724</v>
+        <v>47.20783718</v>
       </c>
       <c r="P48">
-        <v>192.02046896</v>
+        <v>188.83134872</v>
       </c>
       <c r="Q48">
-        <v>243.72046896</v>
+        <v>240.53134872</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1181036261717858</v>
+        <v>0.1193055815565715</v>
       </c>
       <c r="T48">
-        <v>1.486638654977028</v>
+        <v>1.511352122768185</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.308937169728528</v>
+        <v>2.259810846968347</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08628075822498291</v>
+        <v>0.08730235831720148</v>
       </c>
       <c r="C49">
-        <v>3752.747674396681</v>
+        <v>3534.303736584457</v>
       </c>
       <c r="D49">
-        <v>6597.204674396681</v>
+        <v>6443.791736584457</v>
       </c>
       <c r="E49">
-        <v>2770.057</v>
+        <v>2835.088</v>
       </c>
       <c r="F49">
-        <v>3056.457</v>
+        <v>3121.488</v>
       </c>
       <c r="G49">
         <v>212</v>
@@ -5436,45 +5436,45 @@
         <v>423.4</v>
       </c>
       <c r="M49">
-        <v>187.3608141</v>
+        <v>200.0873808</v>
       </c>
       <c r="N49">
-        <v>236.0391859</v>
+        <v>223.3126192</v>
       </c>
       <c r="O49">
-        <v>47.20783718</v>
+        <v>44.66252384</v>
       </c>
       <c r="P49">
-        <v>188.83134872</v>
+        <v>178.65009536</v>
       </c>
       <c r="Q49">
-        <v>240.53134872</v>
+        <v>230.35009536</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1193055815565715</v>
+        <v>0.1205537659946182</v>
       </c>
       <c r="T49">
-        <v>1.511352122768185</v>
+        <v>1.537016108551309</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.259810846968347</v>
+        <v>2.11607547815929</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08730235831720148</v>
+        <v>0.08727115840942007</v>
       </c>
       <c r="C50">
-        <v>3534.303736584457</v>
+        <v>3473.852303952854</v>
       </c>
       <c r="D50">
-        <v>6443.791736584457</v>
+        <v>6448.371303952854</v>
       </c>
       <c r="E50">
-        <v>2835.088</v>
+        <v>2900.119</v>
       </c>
       <c r="F50">
-        <v>3121.488</v>
+        <v>3186.519</v>
       </c>
       <c r="G50">
         <v>212</v>
@@ -5518,28 +5518,28 @@
         <v>423.4</v>
       </c>
       <c r="M50">
-        <v>200.0873808</v>
+        <v>204.2558679</v>
       </c>
       <c r="N50">
-        <v>223.3126192</v>
+        <v>219.1441321</v>
       </c>
       <c r="O50">
-        <v>44.66252384</v>
+        <v>43.82882642</v>
       </c>
       <c r="P50">
-        <v>178.65009536</v>
+        <v>175.31530568</v>
       </c>
       <c r="Q50">
-        <v>230.35009536</v>
+        <v>227.01530568</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1205537659946182</v>
+        <v>0.1218508988420001</v>
       </c>
       <c r="T50">
-        <v>1.537016108551309</v>
+        <v>1.563686525149457</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.11607547815929</v>
+        <v>2.072890264319305</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08727115840942007</v>
+        <v>0.08723995850163865</v>
       </c>
       <c r="C51">
-        <v>3473.852303952854</v>
+        <v>3413.407385297411</v>
       </c>
       <c r="D51">
-        <v>6448.371303952854</v>
+        <v>6452.957385297411</v>
       </c>
       <c r="E51">
-        <v>2900.119</v>
+        <v>2965.15</v>
       </c>
       <c r="F51">
-        <v>3186.519</v>
+        <v>3251.55</v>
       </c>
       <c r="G51">
         <v>212</v>
@@ -5600,28 +5600,28 @@
         <v>423.4</v>
       </c>
       <c r="M51">
-        <v>204.2558679</v>
+        <v>208.424355</v>
       </c>
       <c r="N51">
-        <v>219.1441321</v>
+        <v>214.975645</v>
       </c>
       <c r="O51">
-        <v>43.82882642</v>
+        <v>42.995129</v>
       </c>
       <c r="P51">
-        <v>175.31530568</v>
+        <v>171.980516</v>
       </c>
       <c r="Q51">
-        <v>227.01530568</v>
+        <v>223.680516</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1218508988420001</v>
+        <v>0.1231999170032773</v>
       </c>
       <c r="T51">
-        <v>1.563686525149457</v>
+        <v>1.591423758411532</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.072890264319305</v>
+        <v>2.031432459032919</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08723995850163865</v>
+        <v>0.09039115859385724</v>
       </c>
       <c r="C52">
-        <v>3413.407385297411</v>
+        <v>2915.915627850629</v>
       </c>
       <c r="D52">
-        <v>6452.957385297411</v>
+        <v>6020.496627850629</v>
       </c>
       <c r="E52">
-        <v>2965.15</v>
+        <v>3030.181</v>
       </c>
       <c r="F52">
-        <v>3251.55</v>
+        <v>3316.581</v>
       </c>
       <c r="G52">
         <v>212</v>
@@ -5682,45 +5682,45 @@
         <v>423.4</v>
       </c>
       <c r="M52">
-        <v>208.424355</v>
+        <v>238.4621739</v>
       </c>
       <c r="N52">
-        <v>214.975645</v>
+        <v>184.9378261</v>
       </c>
       <c r="O52">
-        <v>42.995129</v>
+        <v>36.98756522</v>
       </c>
       <c r="P52">
-        <v>171.980516</v>
+        <v>147.95026088</v>
       </c>
       <c r="Q52">
-        <v>223.680516</v>
+        <v>199.65026088</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1231999170032773</v>
+        <v>0.1246039971303209</v>
       </c>
       <c r="T52">
-        <v>1.591423758411532</v>
+        <v>1.620293123643487</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.031432459032919</v>
+        <v>1.775543655731136</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09039115859385724</v>
+        <v>0.09204475868607581</v>
       </c>
       <c r="C53">
-        <v>2915.915627850629</v>
+        <v>2646.351305606758</v>
       </c>
       <c r="D53">
-        <v>6020.496627850629</v>
+        <v>5815.963305606758</v>
       </c>
       <c r="E53">
-        <v>3030.181</v>
+        <v>3095.212</v>
       </c>
       <c r="F53">
-        <v>3316.581</v>
+        <v>3381.612</v>
       </c>
       <c r="G53">
         <v>212</v>
@@ -5764,45 +5764,45 @@
         <v>423.4</v>
       </c>
       <c r="M53">
-        <v>238.4621739</v>
+        <v>256.3261896</v>
       </c>
       <c r="N53">
-        <v>184.9378261</v>
+        <v>167.0738104</v>
       </c>
       <c r="O53">
-        <v>36.98756522</v>
+        <v>33.41476208</v>
       </c>
       <c r="P53">
-        <v>147.95026088</v>
+        <v>133.65904832</v>
       </c>
       <c r="Q53">
-        <v>199.65026088</v>
+        <v>185.35904832</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1246039971303209</v>
+        <v>0.1260665805959913</v>
       </c>
       <c r="T53">
-        <v>1.620293123643487</v>
+        <v>1.650365379093441</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.775543655731136</v>
+        <v>1.651801560584662</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09204475868607581</v>
+        <v>0.0921071587782944</v>
       </c>
       <c r="C54">
-        <v>2646.351305606758</v>
+        <v>2573.873813222729</v>
       </c>
       <c r="D54">
-        <v>5815.963305606758</v>
+        <v>5808.516813222729</v>
       </c>
       <c r="E54">
-        <v>3095.212</v>
+        <v>3160.243</v>
       </c>
       <c r="F54">
-        <v>3381.612</v>
+        <v>3446.643</v>
       </c>
       <c r="G54">
         <v>212</v>
@@ -5846,28 +5846,28 @@
         <v>423.4</v>
       </c>
       <c r="M54">
-        <v>256.3261896</v>
+        <v>261.2555394</v>
       </c>
       <c r="N54">
-        <v>167.0738104</v>
+        <v>162.1444605999999</v>
       </c>
       <c r="O54">
-        <v>33.41476208</v>
+        <v>32.42889211999999</v>
       </c>
       <c r="P54">
-        <v>133.65904832</v>
+        <v>129.7155684799999</v>
       </c>
       <c r="Q54">
-        <v>185.35904832</v>
+        <v>181.41556848</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1260665805959913</v>
+        <v>0.1275914016559455</v>
       </c>
       <c r="T54">
-        <v>1.650365379093441</v>
+        <v>1.681717304988073</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.651801560584662</v>
+        <v>1.620635493403819</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0921071587782944</v>
+        <v>0.09216955887051298</v>
       </c>
       <c r="C55">
-        <v>2573.873813222729</v>
+        <v>2501.415364749657</v>
       </c>
       <c r="D55">
-        <v>5808.516813222729</v>
+        <v>5801.089364749657</v>
       </c>
       <c r="E55">
-        <v>3160.243</v>
+        <v>3225.274</v>
       </c>
       <c r="F55">
-        <v>3446.643</v>
+        <v>3511.674</v>
       </c>
       <c r="G55">
         <v>212</v>
@@ -5928,28 +5928,28 @@
         <v>423.4</v>
       </c>
       <c r="M55">
-        <v>261.2555394</v>
+        <v>266.1848892</v>
       </c>
       <c r="N55">
-        <v>162.1444605999999</v>
+        <v>157.2151107999999</v>
       </c>
       <c r="O55">
-        <v>32.42889211999999</v>
+        <v>31.44302215999999</v>
       </c>
       <c r="P55">
-        <v>129.7155684799999</v>
+        <v>125.77208864</v>
       </c>
       <c r="Q55">
-        <v>181.41556848</v>
+        <v>177.47208864</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1275914016559455</v>
+        <v>0.1291825192837238</v>
       </c>
       <c r="T55">
-        <v>1.681717304988073</v>
+        <v>1.714432358095515</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.620635493403819</v>
+        <v>1.590623725007452</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09216955887051298</v>
+        <v>0.09223195896273156</v>
       </c>
       <c r="C56">
-        <v>2501.415364749657</v>
+        <v>2428.975887225526</v>
       </c>
       <c r="D56">
-        <v>5801.089364749657</v>
+        <v>5793.680887225526</v>
       </c>
       <c r="E56">
-        <v>3225.274</v>
+        <v>3290.305</v>
       </c>
       <c r="F56">
-        <v>3511.674</v>
+        <v>3576.705</v>
       </c>
       <c r="G56">
         <v>212</v>
@@ -6010,28 +6010,28 @@
         <v>423.4</v>
       </c>
       <c r="M56">
-        <v>266.1848892</v>
+        <v>271.114239</v>
       </c>
       <c r="N56">
-        <v>157.2151107999999</v>
+        <v>152.285761</v>
       </c>
       <c r="O56">
-        <v>31.44302215999999</v>
+        <v>30.4571522</v>
       </c>
       <c r="P56">
-        <v>125.77208864</v>
+        <v>121.8286088</v>
       </c>
       <c r="Q56">
-        <v>177.47208864</v>
+        <v>173.5286088</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1291825192837238</v>
+        <v>0.1308443532505146</v>
       </c>
       <c r="T56">
-        <v>1.714432358095515</v>
+        <v>1.748601413563289</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.590623725007452</v>
+        <v>1.561703293643681</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09223195896273156</v>
+        <v>0.09229435905495013</v>
       </c>
       <c r="C57">
-        <v>2428.975887225526</v>
+        <v>2356.555308060566</v>
       </c>
       <c r="D57">
-        <v>5793.680887225526</v>
+        <v>5786.291308060566</v>
       </c>
       <c r="E57">
-        <v>3290.305</v>
+        <v>3355.336</v>
       </c>
       <c r="F57">
-        <v>3576.705</v>
+        <v>3641.736</v>
       </c>
       <c r="G57">
         <v>212</v>
@@ -6092,28 +6092,28 @@
         <v>423.4</v>
       </c>
       <c r="M57">
-        <v>271.114239</v>
+        <v>276.0435888</v>
       </c>
       <c r="N57">
-        <v>152.285761</v>
+        <v>147.3564112</v>
       </c>
       <c r="O57">
-        <v>30.4571522</v>
+        <v>29.47128223999999</v>
       </c>
       <c r="P57">
-        <v>121.8286088</v>
+        <v>117.88512896</v>
       </c>
       <c r="Q57">
-        <v>173.5286088</v>
+        <v>169.58512896</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1308443532505146</v>
+        <v>0.1325817251248867</v>
       </c>
       <c r="T57">
-        <v>1.748601413563289</v>
+        <v>1.784323607915961</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.561703293643681</v>
+        <v>1.533815734828615</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09229435905495013</v>
+        <v>0.0923567591471687</v>
       </c>
       <c r="C58">
-        <v>2356.555308060566</v>
+        <v>2284.153555034868</v>
       </c>
       <c r="D58">
-        <v>5786.291308060566</v>
+        <v>5778.920555034868</v>
       </c>
       <c r="E58">
-        <v>3355.336</v>
+        <v>3420.367</v>
       </c>
       <c r="F58">
-        <v>3641.736</v>
+        <v>3706.767</v>
       </c>
       <c r="G58">
         <v>212</v>
@@ -6174,28 +6174,28 @@
         <v>423.4</v>
       </c>
       <c r="M58">
-        <v>276.0435888</v>
+        <v>280.9729386</v>
       </c>
       <c r="N58">
-        <v>147.3564112</v>
+        <v>142.4270614</v>
       </c>
       <c r="O58">
-        <v>29.47128223999999</v>
+        <v>28.48541227999999</v>
       </c>
       <c r="P58">
-        <v>117.88512896</v>
+        <v>113.94164912</v>
       </c>
       <c r="Q58">
-        <v>169.58512896</v>
+        <v>165.64164912</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1325817251248867</v>
+        <v>0.1343999049934156</v>
       </c>
       <c r="T58">
-        <v>1.784323607915961</v>
+        <v>1.821707299680384</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.533815734828615</v>
+        <v>1.506906686849165</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0923567591471687</v>
+        <v>0.1132813661936379</v>
       </c>
       <c r="C59">
-        <v>2284.153555034868</v>
+        <v>489.4663909536671</v>
       </c>
       <c r="D59">
-        <v>5778.920555034868</v>
+        <v>4049.264390953667</v>
       </c>
       <c r="E59">
-        <v>3420.367</v>
+        <v>3485.398</v>
       </c>
       <c r="F59">
-        <v>3706.767</v>
+        <v>3771.798</v>
       </c>
       <c r="G59">
         <v>212</v>
@@ -6256,45 +6256,45 @@
         <v>423.4</v>
       </c>
       <c r="M59">
-        <v>280.9729386</v>
+        <v>447.3352428000001</v>
       </c>
       <c r="N59">
-        <v>142.4270614</v>
+        <v>-23.93524280000008</v>
       </c>
       <c r="O59">
-        <v>28.48541227999999</v>
+        <v>-4.787048560000017</v>
       </c>
       <c r="P59">
-        <v>113.94164912</v>
+        <v>-19.14819424000007</v>
       </c>
       <c r="Q59">
-        <v>165.64164912</v>
+        <v>32.55180575999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1343999049934156</v>
+        <v>0.1369401148953308</v>
       </c>
       <c r="T59">
-        <v>1.821707299680384</v>
+        <v>1.873936688881006</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.2</v>
+        <v>0.1892987448741206</v>
       </c>
       <c r="W59">
-        <v>0.06064000000000001</v>
+        <v>0.0961491688579293</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.506906686849165</v>
+        <v>0.9464937243706029</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1132813661936379</v>
+        <v>0.1140093661936379</v>
       </c>
       <c r="C60">
-        <v>489.466390953668</v>
+        <v>382.7038697145267</v>
       </c>
       <c r="D60">
-        <v>4049.264390953667</v>
+        <v>4007.532869714526</v>
       </c>
       <c r="E60">
-        <v>3485.397999999999</v>
+        <v>3550.428999999999</v>
       </c>
       <c r="F60">
-        <v>3771.797999999999</v>
+        <v>3836.828999999999</v>
       </c>
       <c r="G60">
         <v>212</v>
@@ -6338,37 +6338,37 @@
         <v>423.4</v>
       </c>
       <c r="M60">
-        <v>447.3352427999999</v>
+        <v>455.0479194</v>
       </c>
       <c r="N60">
-        <v>-23.93524279999997</v>
+        <v>-31.64791939999998</v>
       </c>
       <c r="O60">
-        <v>-4.787048559999994</v>
+        <v>-6.329583879999996</v>
       </c>
       <c r="P60">
-        <v>-19.14819423999997</v>
+        <v>-25.31833551999998</v>
       </c>
       <c r="Q60">
-        <v>32.55180576000007</v>
+        <v>26.38166448000006</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1369401148953307</v>
+        <v>0.1391630445269241</v>
       </c>
       <c r="T60">
-        <v>1.873936688881005</v>
+        <v>1.919642461780542</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1892987448741206</v>
+        <v>0.1860902915711694</v>
       </c>
       <c r="W60">
-        <v>0.0961491688579293</v>
+        <v>0.09652969141965932</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9464937243706031</v>
+        <v>0.9304514578558472</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1140093661936379</v>
+        <v>0.1147373661936379</v>
       </c>
       <c r="C61">
-        <v>382.7038697145267</v>
+        <v>276.7927401180632</v>
       </c>
       <c r="D61">
-        <v>4007.532869714526</v>
+        <v>3966.652740118063</v>
       </c>
       <c r="E61">
-        <v>3550.428999999999</v>
+        <v>3615.46</v>
       </c>
       <c r="F61">
-        <v>3836.828999999999</v>
+        <v>3901.86</v>
       </c>
       <c r="G61">
         <v>212</v>
@@ -6420,37 +6420,37 @@
         <v>423.4</v>
       </c>
       <c r="M61">
-        <v>455.0479194</v>
+        <v>462.760596</v>
       </c>
       <c r="N61">
-        <v>-31.64791939999998</v>
+        <v>-39.36059600000004</v>
       </c>
       <c r="O61">
-        <v>-6.329583879999996</v>
+        <v>-7.872119200000009</v>
       </c>
       <c r="P61">
-        <v>-25.31833551999998</v>
+        <v>-31.48847680000004</v>
       </c>
       <c r="Q61">
-        <v>26.38166448000006</v>
+        <v>20.21152320000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1391630445269241</v>
+        <v>0.1414971206400972</v>
       </c>
       <c r="T61">
-        <v>1.919642461780542</v>
+        <v>1.967633523325055</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1860902915711694</v>
+        <v>0.1829887867116499</v>
       </c>
       <c r="W61">
-        <v>0.09652969141965932</v>
+        <v>0.09689752989599833</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9304514578558472</v>
+        <v>0.9149439335582495</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1147373661936379</v>
+        <v>0.1154653661936379</v>
       </c>
       <c r="C62">
-        <v>276.7927401180632</v>
+        <v>171.7072105757961</v>
       </c>
       <c r="D62">
-        <v>3966.652740118063</v>
+        <v>3926.598210575796</v>
       </c>
       <c r="E62">
-        <v>3615.46</v>
+        <v>3680.491</v>
       </c>
       <c r="F62">
-        <v>3901.86</v>
+        <v>3966.891</v>
       </c>
       <c r="G62">
         <v>212</v>
@@ -6502,37 +6502,37 @@
         <v>423.4</v>
       </c>
       <c r="M62">
-        <v>462.760596</v>
+        <v>470.4732726</v>
       </c>
       <c r="N62">
-        <v>-39.36059600000004</v>
+        <v>-47.0732726</v>
       </c>
       <c r="O62">
-        <v>-7.872119200000009</v>
+        <v>-9.414654519999999</v>
       </c>
       <c r="P62">
-        <v>-31.48847680000004</v>
+        <v>-37.65861808</v>
       </c>
       <c r="Q62">
-        <v>20.21152320000001</v>
+        <v>14.04138192000005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1414971206400972</v>
+        <v>0.1439508929642023</v>
       </c>
       <c r="T62">
-        <v>1.967633523325055</v>
+        <v>2.018085664948775</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1829887867116499</v>
+        <v>0.1799889705360491</v>
       </c>
       <c r="W62">
-        <v>0.09689752989599833</v>
+        <v>0.09725330809442459</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9149439335582495</v>
+        <v>0.8999448526802456</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1154653661936379</v>
+        <v>0.1161933661936379</v>
       </c>
       <c r="C63">
-        <v>171.7072105757961</v>
+        <v>67.42252083982203</v>
       </c>
       <c r="D63">
-        <v>3926.598210575796</v>
+        <v>3887.344520839822</v>
       </c>
       <c r="E63">
-        <v>3680.491</v>
+        <v>3745.521999999999</v>
       </c>
       <c r="F63">
-        <v>3966.891</v>
+        <v>4031.922</v>
       </c>
       <c r="G63">
         <v>212</v>
@@ -6584,37 +6584,37 @@
         <v>423.4</v>
       </c>
       <c r="M63">
-        <v>470.4732726</v>
+        <v>478.1859492</v>
       </c>
       <c r="N63">
-        <v>-47.0732726</v>
+        <v>-54.7859492</v>
       </c>
       <c r="O63">
-        <v>-9.414654519999999</v>
+        <v>-10.95718984</v>
       </c>
       <c r="P63">
-        <v>-37.65861808</v>
+        <v>-43.82875936000001</v>
       </c>
       <c r="Q63">
-        <v>14.04138192000005</v>
+        <v>7.871240640000039</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1439508929642023</v>
+        <v>0.1465338112001024</v>
       </c>
       <c r="T63">
-        <v>2.018085664948775</v>
+        <v>2.071193182447427</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1799889705360491</v>
+        <v>0.1770859226241774</v>
       </c>
       <c r="W63">
-        <v>0.09725330809442459</v>
+        <v>0.09759760957677258</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8999448526802456</v>
+        <v>0.8854296131208867</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1161933661936379</v>
+        <v>0.1169213661936379</v>
       </c>
       <c r="C64">
-        <v>67.42252083982203</v>
+        <v>-36.0851090378319</v>
       </c>
       <c r="D64">
-        <v>3887.344520839822</v>
+        <v>3848.867890962168</v>
       </c>
       <c r="E64">
-        <v>3745.521999999999</v>
+        <v>3810.552999999999</v>
       </c>
       <c r="F64">
-        <v>4031.922</v>
+        <v>4096.953</v>
       </c>
       <c r="G64">
         <v>212</v>
@@ -6666,37 +6666,37 @@
         <v>423.4</v>
       </c>
       <c r="M64">
-        <v>478.1859492</v>
+        <v>485.8986258</v>
       </c>
       <c r="N64">
-        <v>-54.7859492</v>
+        <v>-62.49862580000001</v>
       </c>
       <c r="O64">
-        <v>-10.95718984</v>
+        <v>-12.49972516</v>
       </c>
       <c r="P64">
-        <v>-43.82875936000001</v>
+        <v>-49.99890064000001</v>
       </c>
       <c r="Q64">
-        <v>7.871240640000039</v>
+        <v>1.701099360000036</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1465338112001024</v>
+        <v>0.149256346637943</v>
       </c>
       <c r="T64">
-        <v>2.071193182447427</v>
+        <v>2.127171376567627</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1770859226241774</v>
+        <v>0.1742750349634761</v>
       </c>
       <c r="W64">
-        <v>0.09759760957677258</v>
+        <v>0.09793098085333175</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8854296131208867</v>
+        <v>0.8713751748173806</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1169213661936379</v>
+        <v>0.1176493661936379</v>
       </c>
       <c r="C65">
-        <v>-36.0851090378319</v>
+        <v>-138.8385267443718</v>
       </c>
       <c r="D65">
-        <v>3848.867890962168</v>
+        <v>3811.145473255628</v>
       </c>
       <c r="E65">
-        <v>3810.552999999999</v>
+        <v>3875.583999999999</v>
       </c>
       <c r="F65">
-        <v>4096.953</v>
+        <v>4161.983999999999</v>
       </c>
       <c r="G65">
         <v>212</v>
@@ -6748,37 +6748,37 @@
         <v>423.4</v>
       </c>
       <c r="M65">
-        <v>485.8986258</v>
+        <v>493.6113024</v>
       </c>
       <c r="N65">
-        <v>-62.49862580000001</v>
+        <v>-70.21130240000002</v>
       </c>
       <c r="O65">
-        <v>-12.49972516</v>
+        <v>-14.04226048</v>
       </c>
       <c r="P65">
-        <v>-49.99890064000001</v>
+        <v>-56.16904192000002</v>
       </c>
       <c r="Q65">
-        <v>1.701099360000036</v>
+        <v>-4.469041919999974</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.149256346637943</v>
+        <v>0.1521301340445525</v>
       </c>
       <c r="T65">
-        <v>2.127171376567627</v>
+        <v>2.186259470361173</v>
       </c>
       <c r="U65">
         <v>0.1186</v>
       </c>
       <c r="V65">
-        <v>0.1742750349634761</v>
+        <v>0.1715519875421718</v>
       </c>
       <c r="W65">
-        <v>0.09793098085333175</v>
+        <v>0.09825393427749843</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8713751748173806</v>
+        <v>0.857759937710859</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1176493661936379</v>
+        <v>0.1183773661936379</v>
       </c>
       <c r="C66">
-        <v>-138.8385267443718</v>
+        <v>-240.8596929478663</v>
       </c>
       <c r="D66">
-        <v>3811.145473255628</v>
+        <v>3774.155307052133</v>
       </c>
       <c r="E66">
-        <v>3875.583999999999</v>
+        <v>3940.614999999999</v>
       </c>
       <c r="F66">
-        <v>4161.983999999999</v>
+        <v>4227.014999999999</v>
       </c>
       <c r="G66">
         <v>212</v>
@@ -6830,37 +6830,37 @@
         <v>423.4</v>
       </c>
       <c r="M66">
-        <v>493.6113024</v>
+        <v>501.323979</v>
       </c>
       <c r="N66">
-        <v>-70.21130240000002</v>
+        <v>-77.92397899999997</v>
       </c>
       <c r="O66">
-        <v>-14.04226048</v>
+        <v>-15.58479579999999</v>
       </c>
       <c r="P66">
-        <v>-56.16904192000002</v>
+        <v>-62.33918319999998</v>
       </c>
       <c r="Q66">
-        <v>-4.469041919999974</v>
+        <v>-10.63918319999993</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1521301340445525</v>
+        <v>0.1551681378743969</v>
       </c>
       <c r="T66">
-        <v>2.186259470361173</v>
+        <v>2.248724026657207</v>
       </c>
       <c r="U66">
         <v>0.1186</v>
       </c>
       <c r="V66">
-        <v>0.1715519875421718</v>
+        <v>0.1689127261953692</v>
       </c>
       <c r="W66">
-        <v>0.09825393427749843</v>
+        <v>0.09856695067322924</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.857759937710859</v>
+        <v>0.8445636309768458</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1183773661936379</v>
+        <v>0.1191053661936379</v>
       </c>
       <c r="C67">
-        <v>-240.8596929478663</v>
+        <v>-342.1697239295486</v>
       </c>
       <c r="D67">
-        <v>3774.155307052133</v>
+        <v>3737.876276070452</v>
       </c>
       <c r="E67">
-        <v>3940.614999999999</v>
+        <v>4005.646</v>
       </c>
       <c r="F67">
-        <v>4227.014999999999</v>
+        <v>4292.046</v>
       </c>
       <c r="G67">
         <v>212</v>
@@ -6912,37 +6912,37 @@
         <v>423.4</v>
       </c>
       <c r="M67">
-        <v>501.323979</v>
+        <v>509.0366556000001</v>
       </c>
       <c r="N67">
-        <v>-77.92397899999997</v>
+        <v>-85.6366556000001</v>
       </c>
       <c r="O67">
-        <v>-15.58479579999999</v>
+        <v>-17.12733112000002</v>
       </c>
       <c r="P67">
-        <v>-62.33918319999998</v>
+        <v>-68.50932448000007</v>
       </c>
       <c r="Q67">
-        <v>-10.63918319999993</v>
+        <v>-16.80932448000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1551681378743969</v>
+        <v>0.1583848478118791</v>
       </c>
       <c r="T67">
-        <v>2.248724026657207</v>
+        <v>2.314862968617712</v>
       </c>
       <c r="U67">
         <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.1689127261953692</v>
+        <v>0.1663534424651363</v>
       </c>
       <c r="W67">
-        <v>0.09856695067322924</v>
+        <v>0.09887048172363484</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8445636309768458</v>
+        <v>0.8317672123256813</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1191053661936379</v>
+        <v>0.1198333661936379</v>
       </c>
       <c r="C68">
-        <v>-342.1697239295486</v>
+        <v>-442.7889317807376</v>
       </c>
       <c r="D68">
-        <v>3737.876276070452</v>
+        <v>3702.288068219263</v>
       </c>
       <c r="E68">
-        <v>4005.646</v>
+        <v>4070.677</v>
       </c>
       <c r="F68">
-        <v>4292.046</v>
+        <v>4357.077</v>
       </c>
       <c r="G68">
         <v>212</v>
@@ -6994,37 +6994,37 @@
         <v>423.4</v>
       </c>
       <c r="M68">
-        <v>509.0366556000001</v>
+        <v>516.7493322</v>
       </c>
       <c r="N68">
-        <v>-85.6366556000001</v>
+        <v>-93.34933220000005</v>
       </c>
       <c r="O68">
-        <v>-17.12733112000002</v>
+        <v>-18.66986644000001</v>
       </c>
       <c r="P68">
-        <v>-68.50932448000007</v>
+        <v>-74.67946576000004</v>
       </c>
       <c r="Q68">
-        <v>-16.80932448000003</v>
+        <v>-22.97946576</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1583848478118791</v>
+        <v>0.1617965098667846</v>
       </c>
       <c r="T68">
-        <v>2.314862968617712</v>
+        <v>2.385010331303098</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.1663534424651363</v>
+        <v>0.1638705552641641</v>
       </c>
       <c r="W68">
-        <v>0.09887048172363484</v>
+        <v>0.09916495214567014</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8317672123256813</v>
+        <v>0.8193527763208205</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1198333661936379</v>
+        <v>0.1205613661936379</v>
       </c>
       <c r="C69">
-        <v>-442.7889317807376</v>
+        <v>-542.7368623251145</v>
       </c>
       <c r="D69">
-        <v>3702.288068219263</v>
+        <v>3667.371137674886</v>
       </c>
       <c r="E69">
-        <v>4070.677</v>
+        <v>4135.708000000001</v>
       </c>
       <c r="F69">
-        <v>4357.077</v>
+        <v>4422.108</v>
       </c>
       <c r="G69">
         <v>212</v>
@@ -7076,37 +7076,37 @@
         <v>423.4</v>
       </c>
       <c r="M69">
-        <v>516.7493322</v>
+        <v>524.4620088</v>
       </c>
       <c r="N69">
-        <v>-93.34933220000005</v>
+        <v>-101.0620088000001</v>
       </c>
       <c r="O69">
-        <v>-18.66986644000001</v>
+        <v>-20.21240176000001</v>
       </c>
       <c r="P69">
-        <v>-74.67946576000004</v>
+        <v>-80.84960704000005</v>
       </c>
       <c r="Q69">
-        <v>-22.97946576</v>
+        <v>-29.14960704000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1617965098667846</v>
+        <v>0.1654214008001216</v>
       </c>
       <c r="T69">
-        <v>2.385010331303098</v>
+        <v>2.45954190415632</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.1638705552641641</v>
+        <v>0.1614606941573382</v>
       </c>
       <c r="W69">
-        <v>0.09916495214567014</v>
+        <v>0.0994507616729397</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8193527763208205</v>
+        <v>0.8073034707866907</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1205613661936379</v>
+        <v>0.1799400100341256</v>
       </c>
       <c r="C70">
-        <v>-542.7368623251145</v>
+        <v>-2202.293859775294</v>
       </c>
       <c r="D70">
-        <v>3667.371137674886</v>
+        <v>2072.845140224706</v>
       </c>
       <c r="E70">
-        <v>4135.708000000001</v>
+        <v>4200.739</v>
       </c>
       <c r="F70">
-        <v>4422.108</v>
+        <v>4487.139</v>
       </c>
       <c r="G70">
         <v>212</v>
@@ -7158,45 +7158,45 @@
         <v>423.4</v>
       </c>
       <c r="M70">
-        <v>524.4620088</v>
+        <v>901.0175112000001</v>
       </c>
       <c r="N70">
-        <v>-101.0620088000001</v>
+        <v>-477.6175112000001</v>
       </c>
       <c r="O70">
-        <v>-20.21240176000001</v>
+        <v>-95.52350224000003</v>
       </c>
       <c r="P70">
-        <v>-80.84960704000005</v>
+        <v>-382.0940089600001</v>
       </c>
       <c r="Q70">
-        <v>-29.14960704000001</v>
+        <v>-330.39400896</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1654214008001216</v>
+        <v>0.1755144906339569</v>
       </c>
       <c r="T70">
-        <v>2.45954190415632</v>
+        <v>2.667066454301086</v>
       </c>
       <c r="U70">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1614606941573382</v>
+        <v>0.0939826351290563</v>
       </c>
       <c r="W70">
-        <v>0.0994507616729397</v>
+        <v>0.1819282868660855</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8073034707866907</v>
+        <v>0.4699131756452815</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1799400100341256</v>
+        <v>0.1814900100341256</v>
       </c>
       <c r="C71">
-        <v>-2202.293859775294</v>
+        <v>-2290.586682564599</v>
       </c>
       <c r="D71">
-        <v>2072.845140224706</v>
+        <v>2049.583317435401</v>
       </c>
       <c r="E71">
-        <v>4200.739</v>
+        <v>4265.77</v>
       </c>
       <c r="F71">
-        <v>4487.139</v>
+        <v>4552.17</v>
       </c>
       <c r="G71">
         <v>212</v>
@@ -7240,37 +7240,37 @@
         <v>423.4</v>
       </c>
       <c r="M71">
-        <v>901.0175112000001</v>
+        <v>914.075736</v>
       </c>
       <c r="N71">
-        <v>-477.6175112000001</v>
+        <v>-490.675736</v>
       </c>
       <c r="O71">
-        <v>-95.52350224000003</v>
+        <v>-98.13514720000001</v>
       </c>
       <c r="P71">
-        <v>-382.0940089600001</v>
+        <v>-392.5405888</v>
       </c>
       <c r="Q71">
-        <v>-330.39400896</v>
+        <v>-340.8405888</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1755144906339569</v>
+        <v>0.1798383069884221</v>
       </c>
       <c r="T71">
-        <v>2.667066454301086</v>
+        <v>2.755968669444455</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.0939826351290563</v>
+        <v>0.09264002605578407</v>
       </c>
       <c r="W71">
-        <v>0.1819282868660855</v>
+        <v>0.1821978827679986</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4699131756452815</v>
+        <v>0.4632001302789203</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1814900100341256</v>
+        <v>0.1830400100341256</v>
       </c>
       <c r="C72">
-        <v>-2290.586682564599</v>
+        <v>-2378.363203076369</v>
       </c>
       <c r="D72">
-        <v>2049.583317435401</v>
+        <v>2026.837796923631</v>
       </c>
       <c r="E72">
-        <v>4265.77</v>
+        <v>4330.801</v>
       </c>
       <c r="F72">
-        <v>4552.17</v>
+        <v>4617.201</v>
       </c>
       <c r="G72">
         <v>212</v>
@@ -7322,37 +7322,37 @@
         <v>423.4</v>
       </c>
       <c r="M72">
-        <v>914.075736</v>
+        <v>927.1339608000001</v>
       </c>
       <c r="N72">
-        <v>-490.675736</v>
+        <v>-503.7339608000001</v>
       </c>
       <c r="O72">
-        <v>-98.13514720000001</v>
+        <v>-100.74679216</v>
       </c>
       <c r="P72">
-        <v>-392.5405888</v>
+        <v>-402.98716864</v>
       </c>
       <c r="Q72">
-        <v>-340.8405888</v>
+        <v>-351.28716864</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1798383069884221</v>
+        <v>0.1844603175742297</v>
       </c>
       <c r="T72">
-        <v>2.755968669444455</v>
+        <v>2.851002071839091</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.09264002605578407</v>
+        <v>0.09133523695640683</v>
       </c>
       <c r="W72">
-        <v>0.1821978827679986</v>
+        <v>0.1824598844191535</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4632001302789203</v>
+        <v>0.4566761847820341</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1830400100341256</v>
+        <v>0.1845900100341256</v>
       </c>
       <c r="C73">
-        <v>-2378.363203076367</v>
+        <v>-2465.640421842317</v>
       </c>
       <c r="D73">
-        <v>2026.837796923632</v>
+        <v>2004.591578157683</v>
       </c>
       <c r="E73">
-        <v>4330.800999999999</v>
+        <v>4395.831999999999</v>
       </c>
       <c r="F73">
-        <v>4617.200999999999</v>
+        <v>4682.231999999999</v>
       </c>
       <c r="G73">
         <v>212</v>
@@ -7404,37 +7404,37 @@
         <v>423.4</v>
       </c>
       <c r="M73">
-        <v>927.1339607999998</v>
+        <v>940.1921855999998</v>
       </c>
       <c r="N73">
-        <v>-503.7339607999999</v>
+        <v>-516.7921855999998</v>
       </c>
       <c r="O73">
-        <v>-100.74679216</v>
+        <v>-103.35843712</v>
       </c>
       <c r="P73">
-        <v>-402.9871686399999</v>
+        <v>-413.4337484799998</v>
       </c>
       <c r="Q73">
-        <v>-351.2871686399998</v>
+        <v>-361.7337484799998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1844603175742297</v>
+        <v>0.1894124717733093</v>
       </c>
       <c r="T73">
-        <v>2.85100207183909</v>
+        <v>2.952823574404772</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.09133523695640684</v>
+        <v>0.09006669199867898</v>
       </c>
       <c r="W73">
-        <v>0.1824598844191535</v>
+        <v>0.1827146082466653</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4566761847820342</v>
+        <v>0.4503334599933948</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1845900100341256</v>
+        <v>0.1861400100341256</v>
       </c>
       <c r="C74">
-        <v>-2465.640421842317</v>
+        <v>-2552.434601117847</v>
       </c>
       <c r="D74">
-        <v>2004.591578157683</v>
+        <v>1982.828398882153</v>
       </c>
       <c r="E74">
-        <v>4395.831999999999</v>
+        <v>4460.863</v>
       </c>
       <c r="F74">
-        <v>4682.231999999999</v>
+        <v>4747.263</v>
       </c>
       <c r="G74">
         <v>212</v>
@@ -7486,37 +7486,37 @@
         <v>423.4</v>
       </c>
       <c r="M74">
-        <v>940.1921855999998</v>
+        <v>953.2504104</v>
       </c>
       <c r="N74">
-        <v>-516.7921855999998</v>
+        <v>-529.8504104</v>
       </c>
       <c r="O74">
-        <v>-103.35843712</v>
+        <v>-105.97008208</v>
       </c>
       <c r="P74">
-        <v>-413.4337484799998</v>
+        <v>-423.88032832</v>
       </c>
       <c r="Q74">
-        <v>-361.7337484799998</v>
+        <v>-372.1803283199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1894124717733093</v>
+        <v>0.1947314522093578</v>
       </c>
       <c r="T74">
-        <v>2.952823574404772</v>
+        <v>3.062187410493838</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09006669199867898</v>
+        <v>0.0888329016973272</v>
       </c>
       <c r="W74">
-        <v>0.1827146082466653</v>
+        <v>0.1829623533391767</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4503334599933948</v>
+        <v>0.4441645084866359</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1861400100341256</v>
+        <v>0.1876900100341256</v>
       </c>
       <c r="C75">
-        <v>-2552.434601117847</v>
+        <v>-2638.76130452772</v>
       </c>
       <c r="D75">
-        <v>1982.828398882153</v>
+        <v>1961.53269547228</v>
       </c>
       <c r="E75">
-        <v>4460.863</v>
+        <v>4525.894</v>
       </c>
       <c r="F75">
-        <v>4747.263</v>
+        <v>4812.294</v>
       </c>
       <c r="G75">
         <v>212</v>
@@ -7568,37 +7568,37 @@
         <v>423.4</v>
       </c>
       <c r="M75">
-        <v>953.2504104</v>
+        <v>966.3086352</v>
       </c>
       <c r="N75">
-        <v>-529.8504104</v>
+        <v>-542.9086352</v>
       </c>
       <c r="O75">
-        <v>-105.97008208</v>
+        <v>-108.58172704</v>
       </c>
       <c r="P75">
-        <v>-423.88032832</v>
+        <v>-434.32690816</v>
       </c>
       <c r="Q75">
-        <v>-372.1803283199999</v>
+        <v>-382.62690816</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1947314522093578</v>
+        <v>0.2004595849866408</v>
       </c>
       <c r="T75">
-        <v>3.062187410493838</v>
+        <v>3.179963849358986</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0888329016973272</v>
+        <v>0.08763245707979574</v>
       </c>
       <c r="W75">
-        <v>0.1829623533391767</v>
+        <v>0.183203402618377</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4441645084866359</v>
+        <v>0.4381622853989787</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1876900100341256</v>
+        <v>0.1892400100341256</v>
       </c>
       <c r="C76">
-        <v>-2638.76130452772</v>
+        <v>-2724.6354341841</v>
       </c>
       <c r="D76">
-        <v>1961.53269547228</v>
+        <v>1940.6895658159</v>
       </c>
       <c r="E76">
-        <v>4525.894</v>
+        <v>4590.925</v>
       </c>
       <c r="F76">
-        <v>4812.294</v>
+        <v>4877.325</v>
       </c>
       <c r="G76">
         <v>212</v>
@@ -7650,37 +7650,37 @@
         <v>423.4</v>
       </c>
       <c r="M76">
-        <v>966.3086352</v>
+        <v>979.36686</v>
       </c>
       <c r="N76">
-        <v>-542.9086352</v>
+        <v>-555.96686</v>
       </c>
       <c r="O76">
-        <v>-108.58172704</v>
+        <v>-111.193372</v>
       </c>
       <c r="P76">
-        <v>-434.32690816</v>
+        <v>-444.773488</v>
       </c>
       <c r="Q76">
-        <v>-382.62690816</v>
+        <v>-393.0734879999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2004595849866408</v>
+        <v>0.2066459683861064</v>
       </c>
       <c r="T76">
-        <v>3.179963849358986</v>
+        <v>3.307162403333345</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08763245707979574</v>
+        <v>0.08646402431873179</v>
       </c>
       <c r="W76">
-        <v>0.183203402618377</v>
+        <v>0.1834380239167987</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4381622853989787</v>
+        <v>0.432320121593659</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1892400100341256</v>
+        <v>0.1907900100341256</v>
       </c>
       <c r="C77">
-        <v>-2724.6354341841</v>
+        <v>-2810.071265462981</v>
       </c>
       <c r="D77">
-        <v>1940.6895658159</v>
+        <v>1920.284734537019</v>
       </c>
       <c r="E77">
-        <v>4590.925</v>
+        <v>4655.956</v>
       </c>
       <c r="F77">
-        <v>4877.325</v>
+        <v>4942.356</v>
       </c>
       <c r="G77">
         <v>212</v>
@@ -7732,37 +7732,37 @@
         <v>423.4</v>
       </c>
       <c r="M77">
-        <v>979.36686</v>
+        <v>992.4250848</v>
       </c>
       <c r="N77">
-        <v>-555.96686</v>
+        <v>-569.0250848000001</v>
       </c>
       <c r="O77">
-        <v>-111.193372</v>
+        <v>-113.80501696</v>
       </c>
       <c r="P77">
-        <v>-444.773488</v>
+        <v>-455.2200678400001</v>
       </c>
       <c r="Q77">
-        <v>-393.0734879999999</v>
+        <v>-403.52006784</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2066459683861064</v>
+        <v>0.2133478837355276</v>
       </c>
       <c r="T77">
-        <v>3.307162403333345</v>
+        <v>3.444960836805568</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.08646402431873179</v>
+        <v>0.08532633978822217</v>
       </c>
       <c r="W77">
-        <v>0.1834380239167987</v>
+        <v>0.183666470970525</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.432320121593659</v>
+        <v>0.4266316989411109</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1907900100341256</v>
+        <v>0.1923400100341256</v>
       </c>
       <c r="C78">
-        <v>-2810.071265462981</v>
+        <v>-2895.082479609574</v>
       </c>
       <c r="D78">
-        <v>1920.284734537019</v>
+        <v>1900.304520390426</v>
       </c>
       <c r="E78">
-        <v>4655.956</v>
+        <v>4720.987</v>
       </c>
       <c r="F78">
-        <v>4942.356</v>
+        <v>5007.387</v>
       </c>
       <c r="G78">
         <v>212</v>
@@ -7814,37 +7814,37 @@
         <v>423.4</v>
       </c>
       <c r="M78">
-        <v>992.4250848</v>
+        <v>1005.4833096</v>
       </c>
       <c r="N78">
-        <v>-569.0250848000001</v>
+        <v>-582.0833096</v>
       </c>
       <c r="O78">
-        <v>-113.80501696</v>
+        <v>-116.41666192</v>
       </c>
       <c r="P78">
-        <v>-455.2200678400001</v>
+        <v>-465.66664768</v>
       </c>
       <c r="Q78">
-        <v>-403.52006784</v>
+        <v>-413.9666476799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2133478837355276</v>
+        <v>0.2206325743327244</v>
       </c>
       <c r="T78">
-        <v>3.444960836805568</v>
+        <v>3.594741742753636</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.08532633978822217</v>
+        <v>0.08421820550525824</v>
       </c>
       <c r="W78">
-        <v>0.183666470970525</v>
+        <v>0.1838889843345441</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4266316989411109</v>
+        <v>0.4210910275262912</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1923400100341256</v>
+        <v>0.1938900100341256</v>
       </c>
       <c r="C79">
-        <v>-2895.082479609574</v>
+        <v>-2979.682194329129</v>
       </c>
       <c r="D79">
-        <v>1900.304520390426</v>
+        <v>1880.73580567087</v>
       </c>
       <c r="E79">
-        <v>4720.987</v>
+        <v>4786.018</v>
       </c>
       <c r="F79">
-        <v>5007.387</v>
+        <v>5072.418</v>
       </c>
       <c r="G79">
         <v>212</v>
@@ -7896,37 +7896,37 @@
         <v>423.4</v>
       </c>
       <c r="M79">
-        <v>1005.4833096</v>
+        <v>1018.5415344</v>
       </c>
       <c r="N79">
-        <v>-582.0833096</v>
+        <v>-595.1415344</v>
       </c>
       <c r="O79">
-        <v>-116.41666192</v>
+        <v>-119.02830688</v>
       </c>
       <c r="P79">
-        <v>-465.66664768</v>
+        <v>-476.11322752</v>
       </c>
       <c r="Q79">
-        <v>-413.9666476799999</v>
+        <v>-424.4132275199999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2206325743327244</v>
+        <v>0.2285795095296664</v>
       </c>
       <c r="T79">
-        <v>3.594741742753636</v>
+        <v>3.758139094696984</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.08421820550525824</v>
+        <v>0.08313848492185751</v>
       </c>
       <c r="W79">
-        <v>0.1838889843345441</v>
+        <v>0.184105792227691</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4210910275262912</v>
+        <v>0.4156924246092875</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1938900100341256</v>
+        <v>0.1954400100341256</v>
       </c>
       <c r="C80">
-        <v>-2979.682194329129</v>
+        <v>-3063.882992506933</v>
       </c>
       <c r="D80">
-        <v>1880.73580567087</v>
+        <v>1861.566007493067</v>
       </c>
       <c r="E80">
-        <v>4786.018</v>
+        <v>4851.049</v>
       </c>
       <c r="F80">
-        <v>5072.418</v>
+        <v>5137.449</v>
       </c>
       <c r="G80">
         <v>212</v>
@@ -7978,37 +7978,37 @@
         <v>423.4</v>
       </c>
       <c r="M80">
-        <v>1018.5415344</v>
+        <v>1031.5997592</v>
       </c>
       <c r="N80">
-        <v>-595.1415344</v>
+        <v>-608.1997591999999</v>
       </c>
       <c r="O80">
-        <v>-119.02830688</v>
+        <v>-121.63995184</v>
       </c>
       <c r="P80">
-        <v>-476.11322752</v>
+        <v>-486.5598073599999</v>
       </c>
       <c r="Q80">
-        <v>-424.4132275199999</v>
+        <v>-434.8598073599999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2285795095296664</v>
+        <v>0.2372832956977458</v>
       </c>
       <c r="T80">
-        <v>3.758139094696984</v>
+        <v>3.937098099206364</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08313848492185751</v>
+        <v>0.08208609903677071</v>
       </c>
       <c r="W80">
-        <v>0.184105792227691</v>
+        <v>0.1843171113134165</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4156924246092875</v>
+        <v>0.4104304951838535</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1954400100341256</v>
+        <v>0.1969900100341256</v>
       </c>
       <c r="C81">
-        <v>-3063.882992506933</v>
+        <v>-3147.696949189629</v>
       </c>
       <c r="D81">
-        <v>1861.566007493067</v>
+        <v>1842.783050810371</v>
       </c>
       <c r="E81">
-        <v>4851.049</v>
+        <v>4916.08</v>
       </c>
       <c r="F81">
-        <v>5137.449</v>
+        <v>5202.48</v>
       </c>
       <c r="G81">
         <v>212</v>
@@ -8060,37 +8060,37 @@
         <v>423.4</v>
       </c>
       <c r="M81">
-        <v>1031.5997592</v>
+        <v>1044.657984</v>
       </c>
       <c r="N81">
-        <v>-608.1997591999999</v>
+        <v>-621.257984</v>
       </c>
       <c r="O81">
-        <v>-121.63995184</v>
+        <v>-124.2515968</v>
       </c>
       <c r="P81">
-        <v>-486.5598073599999</v>
+        <v>-497.0063871999999</v>
       </c>
       <c r="Q81">
-        <v>-434.8598073599999</v>
+        <v>-445.3063871999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2372832956977458</v>
+        <v>0.2468574604826331</v>
       </c>
       <c r="T81">
-        <v>3.937098099206364</v>
+        <v>4.133953004166683</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08208609903677071</v>
+        <v>0.08106002279881107</v>
       </c>
       <c r="W81">
-        <v>0.1843171113134165</v>
+        <v>0.1845231474219987</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4104304951838535</v>
+        <v>0.4053001139940553</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1969900100341256</v>
+        <v>0.1985400100341256</v>
       </c>
       <c r="C82">
-        <v>-3147.696949189629</v>
+        <v>-3231.135656949422</v>
       </c>
       <c r="D82">
-        <v>1842.783050810371</v>
+        <v>1824.375343050577</v>
       </c>
       <c r="E82">
-        <v>4916.08</v>
+        <v>4981.111</v>
       </c>
       <c r="F82">
-        <v>5202.48</v>
+        <v>5267.511</v>
       </c>
       <c r="G82">
         <v>212</v>
@@ -8142,37 +8142,37 @@
         <v>423.4</v>
       </c>
       <c r="M82">
-        <v>1044.657984</v>
+        <v>1057.7162088</v>
       </c>
       <c r="N82">
-        <v>-621.257984</v>
+        <v>-634.3162088</v>
       </c>
       <c r="O82">
-        <v>-124.2515968</v>
+        <v>-126.86324176</v>
       </c>
       <c r="P82">
-        <v>-497.0063871999999</v>
+        <v>-507.45296704</v>
       </c>
       <c r="Q82">
-        <v>-445.3063871999999</v>
+        <v>-455.75296704</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2468574604826331</v>
+        <v>0.2574394320869822</v>
       </c>
       <c r="T82">
-        <v>4.133953004166683</v>
+        <v>4.351529478070193</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08106002279881107</v>
+        <v>0.08005928177660351</v>
       </c>
       <c r="W82">
-        <v>0.1845231474219987</v>
+        <v>0.184724096219258</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4053001139940553</v>
+        <v>0.4002964088830175</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1985400100341256</v>
+        <v>0.2000900100341256</v>
       </c>
       <c r="C83">
-        <v>-3231.135656949422</v>
+        <v>-3314.210249743129</v>
       </c>
       <c r="D83">
-        <v>1824.375343050577</v>
+        <v>1806.331750256872</v>
       </c>
       <c r="E83">
-        <v>4981.111</v>
+        <v>5046.142000000001</v>
       </c>
       <c r="F83">
-        <v>5267.511</v>
+        <v>5332.542</v>
       </c>
       <c r="G83">
         <v>212</v>
@@ -8224,37 +8224,37 @@
         <v>423.4</v>
       </c>
       <c r="M83">
-        <v>1057.7162088</v>
+        <v>1070.7744336</v>
       </c>
       <c r="N83">
-        <v>-634.3162088</v>
+        <v>-647.3744336000001</v>
       </c>
       <c r="O83">
-        <v>-126.86324176</v>
+        <v>-129.47488672</v>
       </c>
       <c r="P83">
-        <v>-507.45296704</v>
+        <v>-517.8995468800001</v>
       </c>
       <c r="Q83">
-        <v>-455.75296704</v>
+        <v>-466.1995468800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2574394320869822</v>
+        <v>0.2691971783140368</v>
       </c>
       <c r="T83">
-        <v>4.351529478070193</v>
+        <v>4.593281115740758</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08005928177660351</v>
+        <v>0.07908294907201079</v>
       </c>
       <c r="W83">
-        <v>0.184724096219258</v>
+        <v>0.1849201438263403</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4002964088830175</v>
+        <v>0.3954147453600539</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2000900100341256</v>
+        <v>0.2016400100341256</v>
       </c>
       <c r="C84">
-        <v>-3314.210249743129</v>
+        <v>-3396.931425369249</v>
       </c>
       <c r="D84">
-        <v>1806.331750256872</v>
+        <v>1788.641574630751</v>
       </c>
       <c r="E84">
-        <v>5046.142000000001</v>
+        <v>5111.173000000001</v>
       </c>
       <c r="F84">
-        <v>5332.542</v>
+        <v>5397.573</v>
       </c>
       <c r="G84">
         <v>212</v>
@@ -8306,37 +8306,37 @@
         <v>423.4</v>
       </c>
       <c r="M84">
-        <v>1070.7744336</v>
+        <v>1083.8326584</v>
       </c>
       <c r="N84">
-        <v>-647.3744336000001</v>
+        <v>-660.4326584000002</v>
       </c>
       <c r="O84">
-        <v>-129.47488672</v>
+        <v>-132.08653168</v>
       </c>
       <c r="P84">
-        <v>-517.8995468800001</v>
+        <v>-528.3461267200001</v>
       </c>
       <c r="Q84">
-        <v>-466.1995468800001</v>
+        <v>-476.6461267200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2691971783140368</v>
+        <v>0.2823381888030977</v>
       </c>
       <c r="T84">
-        <v>4.593281115740758</v>
+        <v>4.863474122549039</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.07908294907201079</v>
+        <v>0.07813014245668536</v>
       </c>
       <c r="W84">
-        <v>0.1849201438263403</v>
+        <v>0.1851114673946976</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3954147453600539</v>
+        <v>0.3906507122834267</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2016400100341256</v>
+        <v>0.2031900100341256</v>
       </c>
       <c r="C85">
-        <v>-3396.931425369249</v>
+        <v>-3479.309466618264</v>
       </c>
       <c r="D85">
-        <v>1788.641574630751</v>
+        <v>1771.294533381736</v>
       </c>
       <c r="E85">
-        <v>5111.173000000001</v>
+        <v>5176.204000000001</v>
       </c>
       <c r="F85">
-        <v>5397.573</v>
+        <v>5462.604</v>
       </c>
       <c r="G85">
         <v>212</v>
@@ -8388,37 +8388,37 @@
         <v>423.4</v>
       </c>
       <c r="M85">
-        <v>1083.8326584</v>
+        <v>1096.8908832</v>
       </c>
       <c r="N85">
-        <v>-660.4326584000002</v>
+        <v>-673.4908832000002</v>
       </c>
       <c r="O85">
-        <v>-132.08653168</v>
+        <v>-134.69817664</v>
       </c>
       <c r="P85">
-        <v>-528.3461267200001</v>
+        <v>-538.7927065600002</v>
       </c>
       <c r="Q85">
-        <v>-476.6461267200001</v>
+        <v>-487.0927065600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2823381888030977</v>
+        <v>0.2971218256032915</v>
       </c>
       <c r="T85">
-        <v>4.863474122549039</v>
+        <v>5.167441255208355</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.07813014245668536</v>
+        <v>0.07720002171315338</v>
       </c>
       <c r="W85">
-        <v>0.1851114673946976</v>
+        <v>0.1852982356399988</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3906507122834267</v>
+        <v>0.3860001085657668</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2031900100341256</v>
+        <v>0.2047400100341256</v>
       </c>
       <c r="C86">
-        <v>-3479.309466618262</v>
+        <v>-3561.354261203984</v>
       </c>
       <c r="D86">
-        <v>1771.294533381737</v>
+        <v>1754.280738796016</v>
       </c>
       <c r="E86">
-        <v>5176.204</v>
+        <v>5241.235</v>
       </c>
       <c r="F86">
-        <v>5462.603999999999</v>
+        <v>5527.634999999999</v>
       </c>
       <c r="G86">
         <v>212</v>
@@ -8470,37 +8470,37 @@
         <v>423.4</v>
       </c>
       <c r="M86">
-        <v>1096.8908832</v>
+        <v>1109.949108</v>
       </c>
       <c r="N86">
-        <v>-673.4908832</v>
+        <v>-686.5491079999998</v>
       </c>
       <c r="O86">
-        <v>-134.69817664</v>
+        <v>-137.3098216</v>
       </c>
       <c r="P86">
-        <v>-538.7927065599999</v>
+        <v>-549.2392863999999</v>
       </c>
       <c r="Q86">
-        <v>-487.0927065599999</v>
+        <v>-497.5392863999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2971218256032913</v>
+        <v>0.313876613976844</v>
       </c>
       <c r="T86">
-        <v>5.167441255208351</v>
+        <v>5.511937338888908</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.07720002171315339</v>
+        <v>0.07629178616358689</v>
       </c>
       <c r="W86">
-        <v>0.1852982356399988</v>
+        <v>0.1854806093383518</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3860001085657669</v>
+        <v>0.3814589308179345</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2047400100341256</v>
+        <v>0.2062900100341256</v>
       </c>
       <c r="C87">
-        <v>-3561.354261203984</v>
+        <v>-3643.075320557162</v>
       </c>
       <c r="D87">
-        <v>1754.280738796016</v>
+        <v>1737.590679442837</v>
       </c>
       <c r="E87">
-        <v>5241.235</v>
+        <v>5306.266</v>
       </c>
       <c r="F87">
-        <v>5527.634999999999</v>
+        <v>5592.665999999999</v>
       </c>
       <c r="G87">
         <v>212</v>
@@ -8552,37 +8552,37 @@
         <v>423.4</v>
       </c>
       <c r="M87">
-        <v>1109.949108</v>
+        <v>1123.0073328</v>
       </c>
       <c r="N87">
-        <v>-686.5491079999998</v>
+        <v>-699.6073327999999</v>
       </c>
       <c r="O87">
-        <v>-137.3098216</v>
+        <v>-139.92146656</v>
       </c>
       <c r="P87">
-        <v>-549.2392863999999</v>
+        <v>-559.6858662399999</v>
       </c>
       <c r="Q87">
-        <v>-497.5392863999998</v>
+        <v>-507.9858662399998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.313876613976844</v>
+        <v>0.3330249435466186</v>
       </c>
       <c r="T87">
-        <v>5.511937338888908</v>
+        <v>5.905647148809544</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.07629178616358689</v>
+        <v>0.07540467237098704</v>
       </c>
       <c r="W87">
-        <v>0.1854806093383518</v>
+        <v>0.1856587417879058</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3814589308179345</v>
+        <v>0.3770233618549352</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2062900100341256</v>
+        <v>0.2078400100341256</v>
       </c>
       <c r="C88">
-        <v>-3643.075320557162</v>
+        <v>-3724.48179755641</v>
       </c>
       <c r="D88">
-        <v>1737.590679442837</v>
+        <v>1721.215202443589</v>
       </c>
       <c r="E88">
-        <v>5306.266</v>
+        <v>5371.297</v>
       </c>
       <c r="F88">
-        <v>5592.665999999999</v>
+        <v>5657.696999999999</v>
       </c>
       <c r="G88">
         <v>212</v>
@@ -8634,37 +8634,37 @@
         <v>423.4</v>
       </c>
       <c r="M88">
-        <v>1123.0073328</v>
+        <v>1136.0655576</v>
       </c>
       <c r="N88">
-        <v>-699.6073327999999</v>
+        <v>-712.6655575999999</v>
       </c>
       <c r="O88">
-        <v>-139.92146656</v>
+        <v>-142.53311152</v>
       </c>
       <c r="P88">
-        <v>-559.6858662399999</v>
+        <v>-570.1324460799999</v>
       </c>
       <c r="Q88">
-        <v>-507.9858662399998</v>
+        <v>-518.4324460799999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3330249435466186</v>
+        <v>0.3551191699732816</v>
       </c>
       <c r="T88">
-        <v>5.905647148809544</v>
+        <v>6.359927698717971</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.07540467237098704</v>
+        <v>0.07453795199890673</v>
       </c>
       <c r="W88">
-        <v>0.1856587417879058</v>
+        <v>0.1858327792386195</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3770233618549352</v>
+        <v>0.3726897599945336</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2078400100341256</v>
+        <v>0.2093900100341256</v>
       </c>
       <c r="C89">
-        <v>-3724.48179755641</v>
+        <v>-3805.582503265865</v>
       </c>
       <c r="D89">
-        <v>1721.215202443589</v>
+        <v>1705.145496734134</v>
       </c>
       <c r="E89">
-        <v>5371.297</v>
+        <v>5436.328</v>
       </c>
       <c r="F89">
-        <v>5657.696999999999</v>
+        <v>5722.727999999999</v>
       </c>
       <c r="G89">
         <v>212</v>
@@ -8716,37 +8716,37 @@
         <v>423.4</v>
       </c>
       <c r="M89">
-        <v>1136.0655576</v>
+        <v>1149.1237824</v>
       </c>
       <c r="N89">
-        <v>-712.6655575999999</v>
+        <v>-725.7237823999998</v>
       </c>
       <c r="O89">
-        <v>-142.53311152</v>
+        <v>-145.14475648</v>
       </c>
       <c r="P89">
-        <v>-570.1324460799999</v>
+        <v>-580.5790259199998</v>
       </c>
       <c r="Q89">
-        <v>-518.4324460799999</v>
+        <v>-528.8790259199998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3551191699732816</v>
+        <v>0.3808957674710551</v>
       </c>
       <c r="T89">
-        <v>6.359927698717971</v>
+        <v>6.889921673611136</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.07453795199890673</v>
+        <v>0.07369092981710099</v>
       </c>
       <c r="W89">
-        <v>0.1858327792386195</v>
+        <v>0.1860028612927261</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3726897599945336</v>
+        <v>0.3684546490855048</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2093900100341256</v>
+        <v>0.2109400100341256</v>
       </c>
       <c r="C90">
-        <v>-3805.582503265865</v>
+        <v>-3886.385922743943</v>
       </c>
       <c r="D90">
-        <v>1705.145496734134</v>
+        <v>1689.373077256056</v>
       </c>
       <c r="E90">
-        <v>5436.328</v>
+        <v>5501.359</v>
       </c>
       <c r="F90">
-        <v>5722.727999999999</v>
+        <v>5787.759</v>
       </c>
       <c r="G90">
         <v>212</v>
@@ -8798,37 +8798,37 @@
         <v>423.4</v>
       </c>
       <c r="M90">
-        <v>1149.1237824</v>
+        <v>1162.1820072</v>
       </c>
       <c r="N90">
-        <v>-725.7237823999998</v>
+        <v>-738.7820072000001</v>
       </c>
       <c r="O90">
-        <v>-145.14475648</v>
+        <v>-147.75640144</v>
       </c>
       <c r="P90">
-        <v>-580.5790259199998</v>
+        <v>-591.0256057600001</v>
       </c>
       <c r="Q90">
-        <v>-528.8790259199998</v>
+        <v>-539.32560576</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3808957674710551</v>
+        <v>0.4113590190593329</v>
       </c>
       <c r="T90">
-        <v>6.889921673611136</v>
+        <v>7.516278189393968</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.07369092981710099</v>
+        <v>0.07286294184162792</v>
       </c>
       <c r="W90">
-        <v>0.1860028612927261</v>
+        <v>0.1861691212782011</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3684546490855048</v>
+        <v>0.3643147092081396</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2109400100341256</v>
+        <v>0.2124900100341256</v>
       </c>
       <c r="C91">
-        <v>-3886.385922743943</v>
+        <v>-3966.900229982734</v>
       </c>
       <c r="D91">
-        <v>1689.373077256056</v>
+        <v>1673.889770017266</v>
       </c>
       <c r="E91">
-        <v>5501.359</v>
+        <v>5566.39</v>
       </c>
       <c r="F91">
-        <v>5787.759</v>
+        <v>5852.79</v>
       </c>
       <c r="G91">
         <v>212</v>
@@ -8880,37 +8880,37 @@
         <v>423.4</v>
       </c>
       <c r="M91">
-        <v>1162.1820072</v>
+        <v>1175.240232</v>
       </c>
       <c r="N91">
-        <v>-738.7820072000001</v>
+        <v>-751.8402320000001</v>
       </c>
       <c r="O91">
-        <v>-147.75640144</v>
+        <v>-150.3680464</v>
       </c>
       <c r="P91">
-        <v>-591.0256057600001</v>
+        <v>-601.4721856000001</v>
       </c>
       <c r="Q91">
-        <v>-539.32560576</v>
+        <v>-549.7721856000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4113590190593329</v>
+        <v>0.4479149209652662</v>
       </c>
       <c r="T91">
-        <v>7.516278189393968</v>
+        <v>8.267906008333366</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.07286294184162792</v>
+        <v>0.07205335359894316</v>
       </c>
       <c r="W91">
-        <v>0.1861691212782011</v>
+        <v>0.1863316865973322</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3643147092081396</v>
+        <v>0.3602667679947158</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2124900100341256</v>
+        <v>0.2140400100341256</v>
       </c>
       <c r="C92">
-        <v>-3966.900229982734</v>
+        <v>-4047.13330203335</v>
       </c>
       <c r="D92">
-        <v>1673.889770017266</v>
+        <v>1658.68769796665</v>
       </c>
       <c r="E92">
-        <v>5566.39</v>
+        <v>5631.421</v>
       </c>
       <c r="F92">
-        <v>5852.79</v>
+        <v>5917.821</v>
       </c>
       <c r="G92">
         <v>212</v>
@@ -8962,37 +8962,37 @@
         <v>423.4</v>
       </c>
       <c r="M92">
-        <v>1175.240232</v>
+        <v>1188.2984568</v>
       </c>
       <c r="N92">
-        <v>-751.8402320000001</v>
+        <v>-764.8984568</v>
       </c>
       <c r="O92">
-        <v>-150.3680464</v>
+        <v>-152.97969136</v>
       </c>
       <c r="P92">
-        <v>-601.4721856000001</v>
+        <v>-611.91876544</v>
       </c>
       <c r="Q92">
-        <v>-549.7721856000001</v>
+        <v>-560.21876544</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4479149209652662</v>
+        <v>0.4925943566280735</v>
       </c>
       <c r="T92">
-        <v>8.267906008333366</v>
+        <v>9.186562231481517</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.07205335359894316</v>
+        <v>0.07126155850444929</v>
       </c>
       <c r="W92">
-        <v>0.1863316865973322</v>
+        <v>0.1864906790523066</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3602667679947158</v>
+        <v>0.3563077925222464</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2140400100341256</v>
+        <v>0.2155900100341256</v>
       </c>
       <c r="C93">
-        <v>-4047.13330203335</v>
+        <v>-4127.092732368488</v>
       </c>
       <c r="D93">
-        <v>1658.68769796665</v>
+        <v>1643.759267631511</v>
       </c>
       <c r="E93">
-        <v>5631.421</v>
+        <v>5696.452</v>
       </c>
       <c r="F93">
-        <v>5917.821</v>
+        <v>5982.852</v>
       </c>
       <c r="G93">
         <v>212</v>
@@ -9044,37 +9044,37 @@
         <v>423.4</v>
       </c>
       <c r="M93">
-        <v>1188.2984568</v>
+        <v>1201.3566816</v>
       </c>
       <c r="N93">
-        <v>-764.8984568</v>
+        <v>-777.9566816</v>
       </c>
       <c r="O93">
-        <v>-152.97969136</v>
+        <v>-155.59133632</v>
       </c>
       <c r="P93">
-        <v>-611.91876544</v>
+        <v>-622.36534528</v>
       </c>
       <c r="Q93">
-        <v>-560.21876544</v>
+        <v>-570.66534528</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4925943566280735</v>
+        <v>0.5484436512065829</v>
       </c>
       <c r="T93">
-        <v>9.186562231481517</v>
+        <v>10.33488251041671</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.07126155850444929</v>
+        <v>0.07048697634679223</v>
       </c>
       <c r="W93">
-        <v>0.1864906790523066</v>
+        <v>0.1866462151495641</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3563077925222464</v>
+        <v>0.3524348817339611</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2155900100341256</v>
+        <v>0.2171400100341256</v>
       </c>
       <c r="C94">
-        <v>-4127.092732368488</v>
+        <v>-4206.78584352983</v>
       </c>
       <c r="D94">
-        <v>1643.759267631511</v>
+        <v>1629.097156470169</v>
       </c>
       <c r="E94">
-        <v>5696.452</v>
+        <v>5761.483</v>
       </c>
       <c r="F94">
-        <v>5982.852</v>
+        <v>6047.883</v>
       </c>
       <c r="G94">
         <v>212</v>
@@ -9126,37 +9126,37 @@
         <v>423.4</v>
       </c>
       <c r="M94">
-        <v>1201.3566816</v>
+        <v>1214.4149064</v>
       </c>
       <c r="N94">
-        <v>-777.9566816</v>
+        <v>-791.0149064000001</v>
       </c>
       <c r="O94">
-        <v>-155.59133632</v>
+        <v>-158.20298128</v>
       </c>
       <c r="P94">
-        <v>-622.36534528</v>
+        <v>-632.8119251200001</v>
       </c>
       <c r="Q94">
-        <v>-570.66534528</v>
+        <v>-581.11192512</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5484436512065829</v>
+        <v>0.6202498870932376</v>
       </c>
       <c r="T94">
-        <v>10.33488251041671</v>
+        <v>11.8112942976191</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07048697634679223</v>
+        <v>0.06972905186994499</v>
       </c>
       <c r="W94">
-        <v>0.1866462151495641</v>
+        <v>0.1867984063845151</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3524348817339611</v>
+        <v>0.3486452593497249</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2171400100341256</v>
+        <v>0.2186900100341256</v>
       </c>
       <c r="C95">
-        <v>-4206.78584352983</v>
+        <v>-4286.219699104557</v>
       </c>
       <c r="D95">
-        <v>1629.097156470169</v>
+        <v>1614.694300895444</v>
       </c>
       <c r="E95">
-        <v>5761.483</v>
+        <v>5826.514</v>
       </c>
       <c r="F95">
-        <v>6047.883</v>
+        <v>6112.914</v>
       </c>
       <c r="G95">
         <v>212</v>
@@ -9208,37 +9208,37 @@
         <v>423.4</v>
       </c>
       <c r="M95">
-        <v>1214.4149064</v>
+        <v>1227.4731312</v>
       </c>
       <c r="N95">
-        <v>-791.0149064000001</v>
+        <v>-804.0731311999999</v>
       </c>
       <c r="O95">
-        <v>-158.20298128</v>
+        <v>-160.81462624</v>
       </c>
       <c r="P95">
-        <v>-632.8119251200001</v>
+        <v>-643.25850496</v>
       </c>
       <c r="Q95">
-        <v>-581.11192512</v>
+        <v>-591.5585049599999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6202498870932376</v>
+        <v>0.7159915349421107</v>
       </c>
       <c r="T95">
-        <v>11.8112942976191</v>
+        <v>13.77984334722228</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.06972905186994499</v>
+        <v>0.06898725344579665</v>
       </c>
       <c r="W95">
-        <v>0.1867984063845151</v>
+        <v>0.186947359508084</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3486452593497249</v>
+        <v>0.3449362672289833</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2186900100341256</v>
+        <v>0.2202400100341256</v>
       </c>
       <c r="C96">
-        <v>-4286.219699104557</v>
+        <v>-4365.40111507212</v>
       </c>
       <c r="D96">
-        <v>1614.694300895444</v>
+        <v>1600.54388492788</v>
       </c>
       <c r="E96">
-        <v>5826.514</v>
+        <v>5891.545</v>
       </c>
       <c r="F96">
-        <v>6112.914</v>
+        <v>6177.945</v>
       </c>
       <c r="G96">
         <v>212</v>
@@ -9290,37 +9290,37 @@
         <v>423.4</v>
       </c>
       <c r="M96">
-        <v>1227.4731312</v>
+        <v>1240.531356</v>
       </c>
       <c r="N96">
-        <v>-804.0731311999999</v>
+        <v>-817.131356</v>
       </c>
       <c r="O96">
-        <v>-160.81462624</v>
+        <v>-163.4262712</v>
       </c>
       <c r="P96">
-        <v>-643.25850496</v>
+        <v>-653.7050848</v>
       </c>
       <c r="Q96">
-        <v>-591.5585049599999</v>
+        <v>-602.0050848</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7159915349421107</v>
+        <v>0.8500298419305333</v>
       </c>
       <c r="T96">
-        <v>13.77984334722228</v>
+        <v>16.53581201666675</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.06898725344579665</v>
+        <v>0.06826107183057774</v>
       </c>
       <c r="W96">
-        <v>0.186947359508084</v>
+        <v>0.18709317677642</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3449362672289833</v>
+        <v>0.3413053591528886</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2202400100341256</v>
+        <v>0.2217900100341256</v>
       </c>
       <c r="C97">
-        <v>-4365.40111507212</v>
+        <v>-4444.336670559574</v>
       </c>
       <c r="D97">
-        <v>1600.54388492788</v>
+        <v>1586.639329440426</v>
       </c>
       <c r="E97">
-        <v>5891.545</v>
+        <v>5956.576</v>
       </c>
       <c r="F97">
-        <v>6177.945</v>
+        <v>6242.976</v>
       </c>
       <c r="G97">
         <v>212</v>
@@ -9372,37 +9372,37 @@
         <v>423.4</v>
       </c>
       <c r="M97">
-        <v>1240.531356</v>
+        <v>1253.5895808</v>
       </c>
       <c r="N97">
-        <v>-817.131356</v>
+        <v>-830.1895808</v>
       </c>
       <c r="O97">
-        <v>-163.4262712</v>
+        <v>-166.03791616</v>
       </c>
       <c r="P97">
-        <v>-653.7050848</v>
+        <v>-664.15166464</v>
       </c>
       <c r="Q97">
-        <v>-602.0050848</v>
+        <v>-612.45166464</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8500298419305333</v>
+        <v>1.051087302413167</v>
       </c>
       <c r="T97">
-        <v>16.53581201666675</v>
+        <v>20.66976502083345</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.06826107183057774</v>
+        <v>0.06755001899900921</v>
       </c>
       <c r="W97">
-        <v>0.18709317677642</v>
+        <v>0.1872359561849989</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3413053591528886</v>
+        <v>0.337750094995046</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2217900100341256</v>
+        <v>0.2233400100341256</v>
       </c>
       <c r="C98">
-        <v>-4444.336670559574</v>
+        <v>-4523.032718041119</v>
       </c>
       <c r="D98">
-        <v>1586.639329440426</v>
+        <v>1572.974281958881</v>
       </c>
       <c r="E98">
-        <v>5956.576</v>
+        <v>6021.607</v>
       </c>
       <c r="F98">
-        <v>6242.976</v>
+        <v>6308.007</v>
       </c>
       <c r="G98">
         <v>212</v>
@@ -9454,37 +9454,37 @@
         <v>423.4</v>
       </c>
       <c r="M98">
-        <v>1253.5895808</v>
+        <v>1266.6478056</v>
       </c>
       <c r="N98">
-        <v>-830.1895808</v>
+        <v>-843.2478055999999</v>
       </c>
       <c r="O98">
-        <v>-166.03791616</v>
+        <v>-168.64956112</v>
       </c>
       <c r="P98">
-        <v>-664.15166464</v>
+        <v>-674.5982444799999</v>
       </c>
       <c r="Q98">
-        <v>-612.45166464</v>
+        <v>-622.8982444799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.051087302413164</v>
+        <v>1.386183069884219</v>
       </c>
       <c r="T98">
-        <v>20.66976502083339</v>
+        <v>27.55968669444452</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.06755001899900921</v>
+        <v>0.06685362705056583</v>
       </c>
       <c r="W98">
-        <v>0.1872359561849989</v>
+        <v>0.1873757916882464</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.337750094995046</v>
+        <v>0.3342681352528292</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2233400100341256</v>
+        <v>0.2248900100341256</v>
       </c>
       <c r="C99">
-        <v>-4523.032718041119</v>
+        <v>-4601.495393015076</v>
       </c>
       <c r="D99">
-        <v>1572.974281958881</v>
+        <v>1559.542606984923</v>
       </c>
       <c r="E99">
-        <v>6021.607</v>
+        <v>6086.638</v>
       </c>
       <c r="F99">
-        <v>6308.007</v>
+        <v>6373.038</v>
       </c>
       <c r="G99">
         <v>212</v>
@@ -9536,37 +9536,37 @@
         <v>423.4</v>
       </c>
       <c r="M99">
-        <v>1266.6478056</v>
+        <v>1279.7060304</v>
       </c>
       <c r="N99">
-        <v>-843.2478055999999</v>
+        <v>-856.3060303999999</v>
       </c>
       <c r="O99">
-        <v>-168.64956112</v>
+        <v>-171.26120608</v>
       </c>
       <c r="P99">
-        <v>-674.5982444799999</v>
+        <v>-685.04482432</v>
       </c>
       <c r="Q99">
-        <v>-622.8982444799999</v>
+        <v>-633.3448243199999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.386183069884219</v>
+        <v>2.056374604826329</v>
       </c>
       <c r="T99">
-        <v>27.55968669444452</v>
+        <v>41.33953004166678</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.06685362705056583</v>
+        <v>0.0661714471827029</v>
       </c>
       <c r="W99">
-        <v>0.1873757916882464</v>
+        <v>0.1875127734057133</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3342681352528292</v>
+        <v>0.3308572359135146</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2248900100341256</v>
+        <v>0.2264400100341256</v>
       </c>
       <c r="C100">
-        <v>-4601.495393015076</v>
+        <v>-4679.730623189274</v>
       </c>
       <c r="D100">
-        <v>1559.542606984923</v>
+        <v>1546.338376810725</v>
       </c>
       <c r="E100">
-        <v>6086.638</v>
+        <v>6151.669</v>
       </c>
       <c r="F100">
-        <v>6373.038</v>
+        <v>6438.069</v>
       </c>
       <c r="G100">
         <v>212</v>
@@ -9618,37 +9618,37 @@
         <v>423.4</v>
       </c>
       <c r="M100">
-        <v>1279.7060304</v>
+        <v>1292.7642552</v>
       </c>
       <c r="N100">
-        <v>-856.3060303999999</v>
+        <v>-869.3642552</v>
       </c>
       <c r="O100">
-        <v>-171.26120608</v>
+        <v>-173.87285104</v>
       </c>
       <c r="P100">
-        <v>-685.04482432</v>
+        <v>-695.49140416</v>
       </c>
       <c r="Q100">
-        <v>-633.3448243199999</v>
+        <v>-643.79140416</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.056374604826329</v>
+        <v>4.066949209652658</v>
       </c>
       <c r="T100">
-        <v>41.33953004166678</v>
+        <v>82.67906008333357</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.0661714471827029</v>
+        <v>0.06550304872631196</v>
       </c>
       <c r="W100">
-        <v>0.1875127734057133</v>
+        <v>0.1876469878157566</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3308572359135146</v>
+        <v>0.3275152436315598</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2264400100341256</v>
-      </c>
-      <c r="C101">
-        <v>-4679.730623189274</v>
-      </c>
-      <c r="D101">
-        <v>1546.338376810725</v>
-      </c>
-      <c r="E101">
-        <v>6151.669</v>
-      </c>
-      <c r="F101">
-        <v>6438.069</v>
-      </c>
-      <c r="G101">
-        <v>212</v>
-      </c>
-      <c r="H101">
-        <v>6216.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>475.1</v>
-      </c>
-      <c r="K101">
-        <v>51.70000000000005</v>
-      </c>
-      <c r="L101">
-        <v>423.4</v>
-      </c>
-      <c r="M101">
-        <v>1292.7642552</v>
-      </c>
-      <c r="N101">
-        <v>-869.3642552</v>
-      </c>
-      <c r="O101">
-        <v>-173.87285104</v>
-      </c>
-      <c r="P101">
-        <v>-695.49140416</v>
-      </c>
-      <c r="Q101">
-        <v>-643.79140416</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.066949209652658</v>
-      </c>
-      <c r="T101">
-        <v>82.67906008333357</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.06550304872631196</v>
-      </c>
-      <c r="W101">
-        <v>0.1876469878157566</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3275152436315598</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
